--- a/referencia/formularios/formulario-avancado-loteamento.xlsx
+++ b/referencia/formularios/formulario-avancado-loteamento.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F883"/>
+  <dimension ref="A1:F917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -600,7 +600,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %; nunca 0,04 num campo sem formato). Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
+          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %). O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].nome (tipo = cronograma)</t>
+          <t>fases[1].nome</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].inicio_mes</t>
+          <t>fases[1].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].duracao_meses</t>
+          <t>fases[1].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].nome (tipo = cronograma)</t>
+          <t>fases[2].nome</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].inicio_mes</t>
+          <t>fases[2].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].duracao_meses</t>
+          <t>fases[2].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].nome (tipo = cronograma)</t>
+          <t>fases[3].nome</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].inicio_mes</t>
+          <t>fases[3].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].duracao_meses</t>
+          <t>fases[3].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].nome (tipo = cronograma)</t>
+          <t>fases[4].nome</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].inicio_mes</t>
+          <t>fases[4].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].duracao_meses</t>
+          <t>fases[4].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].nome (tipo = cronograma)</t>
+          <t>fases[5].nome</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].inicio_mes</t>
+          <t>fases[5].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].duracao_meses</t>
+          <t>fases[5].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].nome</t>
+          <t>tipologias[1].nome</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].area_privativa_m2</t>
+          <t>tipologias[1].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].area_privativa_aberta_m2</t>
+          <t>tipologias[1].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].quantidade</t>
+          <t>tipologias[1].quantidade</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].preco_m2</t>
+          <t>tipologias[1].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].nome</t>
+          <t>tipologias[2].nome</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].area_privativa_m2</t>
+          <t>tipologias[2].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].area_privativa_aberta_m2</t>
+          <t>tipologias[2].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].quantidade</t>
+          <t>tipologias[2].quantidade</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].preco_m2</t>
+          <t>tipologias[2].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].nome</t>
+          <t>tipologias[3].nome</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].area_privativa_m2</t>
+          <t>tipologias[3].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].area_privativa_aberta_m2</t>
+          <t>tipologias[3].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].quantidade</t>
+          <t>tipologias[3].quantidade</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].preco_m2</t>
+          <t>tipologias[3].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].nome</t>
+          <t>tipologias[4].nome</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].area_privativa_m2</t>
+          <t>tipologias[4].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].area_privativa_aberta_m2</t>
+          <t>tipologias[4].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].quantidade</t>
+          <t>tipologias[4].quantidade</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].preco_m2</t>
+          <t>tipologias[4].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].nome</t>
+          <t>tipologias[5].nome</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].area_privativa_m2</t>
+          <t>tipologias[5].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].area_privativa_aberta_m2</t>
+          <t>tipologias[5].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].quantidade</t>
+          <t>tipologias[5].quantidade</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].preco_m2</t>
+          <t>tipologias[5].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].nome</t>
+          <t>tipologias[6].nome</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].area_privativa_m2</t>
+          <t>tipologias[6].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].area_privativa_aberta_m2</t>
+          <t>tipologias[6].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].quantidade</t>
+          <t>tipologias[6].quantidade</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].preco_m2</t>
+          <t>tipologias[6].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].nome</t>
+          <t>tipologias[7].nome</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].area_privativa_m2</t>
+          <t>tipologias[7].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].area_privativa_aberta_m2</t>
+          <t>tipologias[7].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].quantidade</t>
+          <t>tipologias[7].quantidade</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].preco_m2</t>
+          <t>tipologias[7].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].nome</t>
+          <t>tipologias[8].nome</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].area_privativa_m2</t>
+          <t>tipologias[8].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].area_privativa_aberta_m2</t>
+          <t>tipologias[8].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].quantidade</t>
+          <t>tipologias[8].quantidade</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].preco_m2</t>
+          <t>tipologias[8].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].nome</t>
+          <t>tipologias[9].nome</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].area_privativa_m2</t>
+          <t>tipologias[9].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].area_privativa_aberta_m2</t>
+          <t>tipologias[9].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].quantidade</t>
+          <t>tipologias[9].quantidade</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].preco_m2</t>
+          <t>tipologias[9].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].nome</t>
+          <t>tipologias[10].nome</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].area_privativa_m2</t>
+          <t>tipologias[10].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].area_privativa_aberta_m2</t>
+          <t>tipologias[10].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].quantidade</t>
+          <t>tipologias[10].quantidade</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].preco_m2</t>
+          <t>tipologias[10].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].nome (tipo = receita)</t>
+          <t>grupos[1].nome</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[1].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[1].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[1].obra_pct</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[1].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[1].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[1].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].nome (tipo = receita)</t>
+          <t>grupos[2].nome</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[2].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[2].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[2].obra_pct</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[2].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[2].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[2].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].nome (tipo = receita)</t>
+          <t>grupos[3].nome</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[3].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[3].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[3].obra_pct</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[3].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[3].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[3].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].nome (tipo = receita)</t>
+          <t>grupos[4].nome</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[4].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[4].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[4].obra_pct</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[4].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[4].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[4].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].nome (tipo = receita)</t>
+          <t>grupos[5].nome</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[5].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[5].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[5].obra_pct</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[5].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[5].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[5].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[1].grupo</t>
+          <t>pagamento[1].grupo</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #1</t>
+          <t>pagamento[1].linha</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>pct #1</t>
+          <t>pagamento[1].pct</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>parcelas #1</t>
+          <t>pagamento[1].parcelas</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #1</t>
+          <t>pagamento[1].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #1</t>
+          <t>pagamento[1].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #1</t>
+          <t>pagamento[1].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[2].grupo</t>
+          <t>pagamento[2].grupo</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #2</t>
+          <t>pagamento[2].linha</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>pct #2</t>
+          <t>pagamento[2].pct</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>parcelas #2</t>
+          <t>pagamento[2].parcelas</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #2</t>
+          <t>pagamento[2].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #2</t>
+          <t>pagamento[2].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #2</t>
+          <t>pagamento[2].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[3].grupo</t>
+          <t>pagamento[3].grupo</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #3</t>
+          <t>pagamento[3].linha</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>pct #3</t>
+          <t>pagamento[3].pct</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>parcelas #3</t>
+          <t>pagamento[3].parcelas</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #3</t>
+          <t>pagamento[3].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #3</t>
+          <t>pagamento[3].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #3</t>
+          <t>pagamento[3].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[4].grupo</t>
+          <t>pagamento[4].grupo</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #4</t>
+          <t>pagamento[4].linha</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>pct #4</t>
+          <t>pagamento[4].pct</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>parcelas #4</t>
+          <t>pagamento[4].parcelas</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #4</t>
+          <t>pagamento[4].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #4</t>
+          <t>pagamento[4].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #4</t>
+          <t>pagamento[4].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[5].grupo</t>
+          <t>pagamento[5].grupo</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #5</t>
+          <t>pagamento[5].linha</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>pct #5</t>
+          <t>pagamento[5].pct</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>parcelas #5</t>
+          <t>pagamento[5].parcelas</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #5</t>
+          <t>pagamento[5].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #5</t>
+          <t>pagamento[5].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #5</t>
+          <t>pagamento[5].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[6].grupo</t>
+          <t>pagamento[6].grupo</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #6</t>
+          <t>pagamento[6].linha</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>pct #6</t>
+          <t>pagamento[6].pct</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>parcelas #6</t>
+          <t>pagamento[6].parcelas</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #6</t>
+          <t>pagamento[6].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #6</t>
+          <t>pagamento[6].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #6</t>
+          <t>pagamento[6].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[7].grupo</t>
+          <t>pagamento[7].grupo</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #7</t>
+          <t>pagamento[7].linha</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>pct #7</t>
+          <t>pagamento[7].pct</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>parcelas #7</t>
+          <t>pagamento[7].parcelas</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #7</t>
+          <t>pagamento[7].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #7</t>
+          <t>pagamento[7].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #7</t>
+          <t>pagamento[7].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[8].grupo</t>
+          <t>pagamento[8].grupo</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #8</t>
+          <t>pagamento[8].linha</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>pct #8</t>
+          <t>pagamento[8].pct</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>parcelas #8</t>
+          <t>pagamento[8].parcelas</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #8</t>
+          <t>pagamento[8].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #8</t>
+          <t>pagamento[8].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #8</t>
+          <t>pagamento[8].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[9].grupo</t>
+          <t>pagamento[9].grupo</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #9</t>
+          <t>pagamento[9].linha</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>pct #9</t>
+          <t>pagamento[9].pct</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>parcelas #9</t>
+          <t>pagamento[9].parcelas</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #9</t>
+          <t>pagamento[9].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #9</t>
+          <t>pagamento[9].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #9</t>
+          <t>pagamento[9].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[10].grupo</t>
+          <t>pagamento[10].grupo</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #10</t>
+          <t>pagamento[10].linha</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>pct #10</t>
+          <t>pagamento[10].pct</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>parcelas #10</t>
+          <t>pagamento[10].parcelas</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #10</t>
+          <t>pagamento[10].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #10</t>
+          <t>pagamento[10].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #10</t>
+          <t>pagamento[10].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].fase_id</t>
+          <t>alocacoes[1].grupo</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].tipologia_id</t>
+          <t>alocacoes[1].tipologia</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].unidades</t>
+          <t>alocacoes[1].unidades</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].preco_m2</t>
+          <t>alocacoes[1].preco_m2</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].fase_id</t>
+          <t>alocacoes[2].grupo</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].tipologia_id</t>
+          <t>alocacoes[2].tipologia</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].unidades</t>
+          <t>alocacoes[2].unidades</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].preco_m2</t>
+          <t>alocacoes[2].preco_m2</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].fase_id</t>
+          <t>alocacoes[3].grupo</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].tipologia_id</t>
+          <t>alocacoes[3].tipologia</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].unidades</t>
+          <t>alocacoes[3].unidades</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].preco_m2</t>
+          <t>alocacoes[3].preco_m2</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].fase_id</t>
+          <t>alocacoes[4].grupo</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].tipologia_id</t>
+          <t>alocacoes[4].tipologia</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].unidades</t>
+          <t>alocacoes[4].unidades</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].preco_m2</t>
+          <t>alocacoes[4].preco_m2</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].fase_id</t>
+          <t>alocacoes[5].grupo</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].tipologia_id</t>
+          <t>alocacoes[5].tipologia</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].unidades</t>
+          <t>alocacoes[5].unidades</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].preco_m2</t>
+          <t>alocacoes[5].preco_m2</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].fase_id</t>
+          <t>alocacoes[6].grupo</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].tipologia_id</t>
+          <t>alocacoes[6].tipologia</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].unidades</t>
+          <t>alocacoes[6].unidades</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].preco_m2</t>
+          <t>alocacoes[6].preco_m2</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].fase_id</t>
+          <t>alocacoes[7].grupo</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].tipologia_id</t>
+          <t>alocacoes[7].tipologia</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].unidades</t>
+          <t>alocacoes[7].unidades</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].preco_m2</t>
+          <t>alocacoes[7].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].fase_id</t>
+          <t>alocacoes[8].grupo</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].tipologia_id</t>
+          <t>alocacoes[8].tipologia</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].unidades</t>
+          <t>alocacoes[8].unidades</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].preco_m2</t>
+          <t>alocacoes[8].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].fase_id</t>
+          <t>alocacoes[9].grupo</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].tipologia_id</t>
+          <t>alocacoes[9].tipologia</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].unidades</t>
+          <t>alocacoes[9].unidades</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].preco_m2</t>
+          <t>alocacoes[9].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].fase_id</t>
+          <t>alocacoes[10].grupo</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].tipologia_id</t>
+          <t>alocacoes[10].tipologia</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].unidades</t>
+          <t>alocacoes[10].unidades</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].preco_m2</t>
+          <t>alocacoes[10].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].grupo</t>
+          <t>custos[1].grupo</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].categoria</t>
+          <t>custos[1].categoria</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].subcategoria</t>
+          <t>custos[1].subcategoria</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_unidade</t>
+          <t>custos[1].unidade</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[1].valor_rs</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[1].valor_pct</t>
         </is>
       </c>
     </row>
@@ -5434,12 +5434,12 @@
       <c r="B302" s="6" t="n"/>
       <c r="C302" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].curva_id / distribuicao_modo</t>
+          <t>custos[1].distribuicao</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].cronograma_evento / fase_ancora_id</t>
+          <t>custos[1].cronograma</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].inicio_mes</t>
+          <t>custos[1].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].duracao_meses</t>
+          <t>custos[1].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].grupo</t>
+          <t>custos[2].grupo</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].categoria</t>
+          <t>custos[2].categoria</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].subcategoria</t>
+          <t>custos[2].subcategoria</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_unidade</t>
+          <t>custos[2].unidade</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[2].valor_rs</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[2].valor_pct</t>
         </is>
       </c>
     </row>
@@ -5627,12 +5627,12 @@
       <c r="B313" s="6" t="n"/>
       <c r="C313" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].curva_id / distribuicao_modo</t>
+          <t>custos[2].distribuicao</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D314" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].cronograma_evento / fase_ancora_id</t>
+          <t>custos[2].cronograma</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].inicio_mes</t>
+          <t>custos[2].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].duracao_meses</t>
+          <t>custos[2].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="D318" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].grupo</t>
+          <t>custos[3].grupo</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].categoria</t>
+          <t>custos[3].categoria</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].subcategoria</t>
+          <t>custos[3].subcategoria</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_unidade</t>
+          <t>custos[3].unidade</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="D322" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[3].valor_rs</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[3].valor_pct</t>
         </is>
       </c>
     </row>
@@ -5824,12 +5824,12 @@
       <c r="B324" s="6" t="n"/>
       <c r="C324" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D324" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].curva_id / distribuicao_modo</t>
+          <t>custos[3].distribuicao</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].cronograma_evento / fase_ancora_id</t>
+          <t>custos[3].cronograma</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="D326" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].inicio_mes</t>
+          <t>custos[3].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].duracao_meses</t>
+          <t>custos[3].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].grupo</t>
+          <t>custos[4].grupo</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D330" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].categoria</t>
+          <t>custos[4].categoria</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].subcategoria</t>
+          <t>custos[4].subcategoria</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_unidade</t>
+          <t>custos[4].unidade</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[4].valor_rs</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[4].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6009,12 +6009,12 @@
       <c r="B335" s="6" t="n"/>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].curva_id / distribuicao_modo</t>
+          <t>custos[4].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].cronograma_evento / fase_ancora_id</t>
+          <t>custos[4].cronograma</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].inicio_mes</t>
+          <t>custos[4].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="D338" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].duracao_meses</t>
+          <t>custos[4].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="D340" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].grupo</t>
+          <t>custos[5].grupo</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].categoria</t>
+          <t>custos[5].categoria</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="D342" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].subcategoria</t>
+          <t>custos[5].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_unidade</t>
+          <t>custos[5].unidade</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="D344" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[5].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[5].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       <c r="B346" s="6" t="n"/>
       <c r="C346" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D346" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].curva_id / distribuicao_modo</t>
+          <t>custos[5].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].cronograma_evento / fase_ancora_id</t>
+          <t>custos[5].cronograma</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="D348" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].inicio_mes</t>
+          <t>custos[5].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].duracao_meses</t>
+          <t>custos[5].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].grupo</t>
+          <t>custos[6].grupo</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="D352" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].categoria</t>
+          <t>custos[6].categoria</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].subcategoria</t>
+          <t>custos[6].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D354" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_unidade</t>
+          <t>custos[6].unidade</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[6].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="D356" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[6].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6379,12 +6379,12 @@
       <c r="B357" s="6" t="n"/>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].curva_id / distribuicao_modo</t>
+          <t>custos[6].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="D358" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].cronograma_evento / fase_ancora_id</t>
+          <t>custos[6].cronograma</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].inicio_mes</t>
+          <t>custos[6].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D360" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].duracao_meses</t>
+          <t>custos[6].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="D362" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].grupo</t>
+          <t>custos[7].grupo</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].categoria</t>
+          <t>custos[7].categoria</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="D364" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].subcategoria</t>
+          <t>custos[7].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_unidade</t>
+          <t>custos[7].unidade</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="D366" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[7].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[7].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6564,12 +6564,12 @@
       <c r="B368" s="6" t="n"/>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D368" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].curva_id / distribuicao_modo</t>
+          <t>custos[7].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].cronograma_evento / fase_ancora_id</t>
+          <t>custos[7].cronograma</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="D370" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].inicio_mes</t>
+          <t>custos[7].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].duracao_meses</t>
+          <t>custos[7].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].grupo</t>
+          <t>custos[8].grupo</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="D374" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].categoria</t>
+          <t>custos[8].categoria</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].subcategoria</t>
+          <t>custos[8].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="D376" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_unidade</t>
+          <t>custos[8].unidade</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[8].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="D378" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[8].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       <c r="B379" s="6" t="n"/>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].curva_id / distribuicao_modo</t>
+          <t>custos[8].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="D380" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].cronograma_evento / fase_ancora_id</t>
+          <t>custos[8].cronograma</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].inicio_mes</t>
+          <t>custos[8].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="D382" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].duracao_meses</t>
+          <t>custos[8].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="D384" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].grupo</t>
+          <t>custos[9].grupo</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].categoria</t>
+          <t>custos[9].categoria</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="D386" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].subcategoria</t>
+          <t>custos[9].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_unidade</t>
+          <t>custos[9].unidade</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D388" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[9].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[9].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6934,12 +6934,12 @@
       <c r="B390" s="6" t="n"/>
       <c r="C390" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D390" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].curva_id / distribuicao_modo</t>
+          <t>custos[9].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].cronograma_evento / fase_ancora_id</t>
+          <t>custos[9].cronograma</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="D392" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].inicio_mes</t>
+          <t>custos[9].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].duracao_meses</t>
+          <t>custos[9].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].grupo</t>
+          <t>custos[10].grupo</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="D396" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].categoria</t>
+          <t>custos[10].categoria</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].subcategoria</t>
+          <t>custos[10].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="D398" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_unidade</t>
+          <t>custos[10].unidade</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[10].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="D400" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[10].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7119,12 +7119,12 @@
       <c r="B401" s="6" t="n"/>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].curva_id / distribuicao_modo</t>
+          <t>custos[10].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="D402" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].cronograma_evento / fase_ancora_id</t>
+          <t>custos[10].cronograma</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].inicio_mes</t>
+          <t>custos[10].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D404" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].duracao_meses</t>
+          <t>custos[10].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="D406" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].grupo</t>
+          <t>custos[11].grupo</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].categoria</t>
+          <t>custos[11].categoria</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D408" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].subcategoria</t>
+          <t>custos[11].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_unidade</t>
+          <t>custos[11].unidade</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="D410" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[11].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[11].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       <c r="B412" s="6" t="n"/>
       <c r="C412" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D412" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].curva_id / distribuicao_modo</t>
+          <t>custos[11].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].cronograma_evento / fase_ancora_id</t>
+          <t>custos[11].cronograma</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="D414" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].inicio_mes</t>
+          <t>custos[11].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].duracao_meses</t>
+          <t>custos[11].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].grupo</t>
+          <t>custos[12].grupo</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="D418" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].categoria</t>
+          <t>custos[12].categoria</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].subcategoria</t>
+          <t>custos[12].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D420" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_unidade</t>
+          <t>custos[12].unidade</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[12].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="D422" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[12].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       <c r="B423" s="6" t="n"/>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].curva_id / distribuicao_modo</t>
+          <t>custos[12].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="D424" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].cronograma_evento / fase_ancora_id</t>
+          <t>custos[12].cronograma</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].inicio_mes</t>
+          <t>custos[12].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="D426" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].duracao_meses</t>
+          <t>custos[12].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="D428" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].grupo</t>
+          <t>custos[13].grupo</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].categoria</t>
+          <t>custos[13].categoria</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D430" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].subcategoria</t>
+          <t>custos[13].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_unidade</t>
+          <t>custos[13].unidade</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="D432" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[13].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[13].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       <c r="B434" s="6" t="n"/>
       <c r="C434" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D434" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].curva_id / distribuicao_modo</t>
+          <t>custos[13].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].cronograma_evento / fase_ancora_id</t>
+          <t>custos[13].cronograma</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="D436" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].inicio_mes</t>
+          <t>custos[13].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].duracao_meses</t>
+          <t>custos[13].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].grupo</t>
+          <t>custos[14].grupo</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="D440" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].categoria</t>
+          <t>custos[14].categoria</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].subcategoria</t>
+          <t>custos[14].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="D442" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_unidade</t>
+          <t>custos[14].unidade</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[14].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="D444" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[14].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       <c r="B445" s="6" t="n"/>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].curva_id / distribuicao_modo</t>
+          <t>custos[14].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="D446" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].cronograma_evento / fase_ancora_id</t>
+          <t>custos[14].cronograma</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].inicio_mes</t>
+          <t>custos[14].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D448" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].duracao_meses</t>
+          <t>custos[14].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="D450" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].grupo</t>
+          <t>custos[15].grupo</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].categoria</t>
+          <t>custos[15].categoria</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="D452" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].subcategoria</t>
+          <t>custos[15].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_unidade</t>
+          <t>custos[15].unidade</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D454" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[15].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[15].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8044,12 +8044,12 @@
       <c r="B456" s="6" t="n"/>
       <c r="C456" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D456" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].curva_id / distribuicao_modo</t>
+          <t>custos[15].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].cronograma_evento / fase_ancora_id</t>
+          <t>custos[15].cronograma</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="D458" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].inicio_mes</t>
+          <t>custos[15].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].duracao_meses</t>
+          <t>custos[15].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].grupo</t>
+          <t>custos[16].grupo</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D462" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].categoria</t>
+          <t>custos[16].categoria</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].subcategoria</t>
+          <t>custos[16].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="D464" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_unidade</t>
+          <t>custos[16].unidade</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D465" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[16].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="D466" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[16].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8229,12 +8229,12 @@
       <c r="B467" s="6" t="n"/>
       <c r="C467" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D467" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].curva_id / distribuicao_modo</t>
+          <t>custos[16].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="D468" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].cronograma_evento / fase_ancora_id</t>
+          <t>custos[16].cronograma</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D469" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].inicio_mes</t>
+          <t>custos[16].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="D470" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].duracao_meses</t>
+          <t>custos[16].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="D472" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].grupo</t>
+          <t>custos[17].grupo</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D473" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].categoria</t>
+          <t>custos[17].categoria</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="D474" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].subcategoria</t>
+          <t>custos[17].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D475" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_unidade</t>
+          <t>custos[17].unidade</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="D476" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[17].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="D477" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[17].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8414,12 @@
       <c r="B478" s="6" t="n"/>
       <c r="C478" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D478" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].curva_id / distribuicao_modo</t>
+          <t>custos[17].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="D479" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].cronograma_evento / fase_ancora_id</t>
+          <t>custos[17].cronograma</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="D480" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].inicio_mes</t>
+          <t>custos[17].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="D481" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].duracao_meses</t>
+          <t>custos[17].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D483" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].grupo</t>
+          <t>custos[18].grupo</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="D484" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].categoria</t>
+          <t>custos[18].categoria</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="D485" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].subcategoria</t>
+          <t>custos[18].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D486" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_unidade</t>
+          <t>custos[18].unidade</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="D487" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[18].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D488" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[18].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8599,12 +8599,12 @@
       <c r="B489" s="6" t="n"/>
       <c r="C489" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D489" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].curva_id / distribuicao_modo</t>
+          <t>custos[18].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="D490" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].cronograma_evento / fase_ancora_id</t>
+          <t>custos[18].cronograma</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="D491" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].inicio_mes</t>
+          <t>custos[18].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="D492" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].duracao_meses</t>
+          <t>custos[18].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="D494" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].grupo</t>
+          <t>custos[19].grupo</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="D495" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].categoria</t>
+          <t>custos[19].categoria</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D496" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].subcategoria</t>
+          <t>custos[19].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="D497" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_unidade</t>
+          <t>custos[19].unidade</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D498" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[19].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D499" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[19].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8784,12 +8784,12 @@
       <c r="B500" s="6" t="n"/>
       <c r="C500" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D500" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].curva_id / distribuicao_modo</t>
+          <t>custos[19].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="D501" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].cronograma_evento / fase_ancora_id</t>
+          <t>custos[19].cronograma</t>
         </is>
       </c>
     </row>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D502" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].inicio_mes</t>
+          <t>custos[19].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="D503" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].duracao_meses</t>
+          <t>custos[19].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D505" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].grupo</t>
+          <t>custos[20].grupo</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D506" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].categoria</t>
+          <t>custos[20].categoria</t>
         </is>
       </c>
     </row>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D507" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].subcategoria</t>
+          <t>custos[20].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="D508" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_unidade</t>
+          <t>custos[20].unidade</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="D509" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[20].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D510" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[20].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
       <c r="B511" s="6" t="n"/>
       <c r="C511" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D511" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].curva_id / distribuicao_modo</t>
+          <t>custos[20].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="D512" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].cronograma_evento / fase_ancora_id</t>
+          <t>custos[20].cronograma</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D513" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].inicio_mes</t>
+          <t>custos[20].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D514" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].duracao_meses</t>
+          <t>custos[20].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="D516" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].grupo</t>
+          <t>custos[21].grupo</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="D517" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].categoria</t>
+          <t>custos[21].categoria</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="D518" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].subcategoria</t>
+          <t>custos[21].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D519" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_unidade</t>
+          <t>custos[21].unidade</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="D520" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[21].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D521" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[21].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9154,12 +9154,12 @@
       <c r="B522" s="6" t="n"/>
       <c r="C522" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D522" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].curva_id / distribuicao_modo</t>
+          <t>custos[21].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="D523" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].cronograma_evento / fase_ancora_id</t>
+          <t>custos[21].cronograma</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="D524" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].inicio_mes</t>
+          <t>custos[21].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="D525" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].duracao_meses</t>
+          <t>custos[21].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="D527" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].grupo</t>
+          <t>custos[22].grupo</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D528" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].categoria</t>
+          <t>custos[22].categoria</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="D529" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].subcategoria</t>
+          <t>custos[22].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="D530" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_unidade</t>
+          <t>custos[22].unidade</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="D531" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[22].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="D532" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[22].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9339,12 +9339,12 @@
       <c r="B533" s="6" t="n"/>
       <c r="C533" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D533" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].curva_id / distribuicao_modo</t>
+          <t>custos[22].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="D534" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].cronograma_evento / fase_ancora_id</t>
+          <t>custos[22].cronograma</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="D535" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].inicio_mes</t>
+          <t>custos[22].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D536" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].duracao_meses</t>
+          <t>custos[22].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D538" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].grupo</t>
+          <t>custos[23].grupo</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="D539" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].categoria</t>
+          <t>custos[23].categoria</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D540" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].subcategoria</t>
+          <t>custos[23].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="D541" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_unidade</t>
+          <t>custos[23].unidade</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D542" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[23].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D543" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[23].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       <c r="B544" s="6" t="n"/>
       <c r="C544" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D544" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].curva_id / distribuicao_modo</t>
+          <t>custos[23].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="D545" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].cronograma_evento / fase_ancora_id</t>
+          <t>custos[23].cronograma</t>
         </is>
       </c>
     </row>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="D546" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].inicio_mes</t>
+          <t>custos[23].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="D547" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].duracao_meses</t>
+          <t>custos[23].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D549" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].grupo</t>
+          <t>custos[24].grupo</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="D550" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].categoria</t>
+          <t>custos[24].categoria</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="D551" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].subcategoria</t>
+          <t>custos[24].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="D552" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_unidade</t>
+          <t>custos[24].unidade</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D553" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[24].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="D554" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[24].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9709,12 @@
       <c r="B555" s="6" t="n"/>
       <c r="C555" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D555" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].curva_id / distribuicao_modo</t>
+          <t>custos[24].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="D556" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].cronograma_evento / fase_ancora_id</t>
+          <t>custos[24].cronograma</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D557" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].inicio_mes</t>
+          <t>custos[24].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="D558" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].duracao_meses</t>
+          <t>custos[24].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="D560" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].grupo</t>
+          <t>custos[25].grupo</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D561" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].categoria</t>
+          <t>custos[25].categoria</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="D562" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].subcategoria</t>
+          <t>custos[25].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="D563" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_unidade</t>
+          <t>custos[25].unidade</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="D564" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[25].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D565" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[25].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       <c r="B566" s="6" t="n"/>
       <c r="C566" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D566" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].curva_id / distribuicao_modo</t>
+          <t>custos[25].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="D567" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].cronograma_evento / fase_ancora_id</t>
+          <t>custos[25].cronograma</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="D568" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].inicio_mes</t>
+          <t>custos[25].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="D569" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].duracao_meses</t>
+          <t>custos[25].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="D571" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].grupo</t>
+          <t>custos[26].grupo</t>
         </is>
       </c>
     </row>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="D572" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].categoria</t>
+          <t>custos[26].categoria</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D573" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].subcategoria</t>
+          <t>custos[26].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="D574" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_unidade</t>
+          <t>custos[26].unidade</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="D575" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[26].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="D576" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[26].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       <c r="B577" s="6" t="n"/>
       <c r="C577" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D577" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].curva_id / distribuicao_modo</t>
+          <t>custos[26].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D578" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].cronograma_evento / fase_ancora_id</t>
+          <t>custos[26].cronograma</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="D579" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].inicio_mes</t>
+          <t>custos[26].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="D580" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].duracao_meses</t>
+          <t>custos[26].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="D582" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].grupo</t>
+          <t>custos[27].grupo</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D583" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].categoria</t>
+          <t>custos[27].categoria</t>
         </is>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="D584" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].subcategoria</t>
+          <t>custos[27].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="D585" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_unidade</t>
+          <t>custos[27].unidade</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="D586" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[27].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="D587" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[27].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10264,12 +10264,12 @@
       <c r="B588" s="6" t="n"/>
       <c r="C588" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D588" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].curva_id / distribuicao_modo</t>
+          <t>custos[27].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="D589" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].cronograma_evento / fase_ancora_id</t>
+          <t>custos[27].cronograma</t>
         </is>
       </c>
     </row>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="D590" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].inicio_mes</t>
+          <t>custos[27].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="D591" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].duracao_meses</t>
+          <t>custos[27].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D593" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].grupo</t>
+          <t>custos[28].grupo</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D594" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].categoria</t>
+          <t>custos[28].categoria</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="D595" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].subcategoria</t>
+          <t>custos[28].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="D596" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_unidade</t>
+          <t>custos[28].unidade</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="D597" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[28].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="D598" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[28].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10449,12 +10449,12 @@
       <c r="B599" s="6" t="n"/>
       <c r="C599" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D599" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].curva_id / distribuicao_modo</t>
+          <t>custos[28].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D600" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].cronograma_evento / fase_ancora_id</t>
+          <t>custos[28].cronograma</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="D601" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].inicio_mes</t>
+          <t>custos[28].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="D602" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].duracao_meses</t>
+          <t>custos[28].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D604" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#1].permuta_tipologia_id</t>
+          <t>permuta_fisica[1].tipologia</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="D605" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#1].permuta_quantidade</t>
+          <t>permuta_fisica[1].unidades</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="D606" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#2].permuta_tipologia_id</t>
+          <t>permuta_fisica[2].tipologia</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D607" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#2].permuta_quantidade</t>
+          <t>permuta_fisica[2].unidades</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="D609" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_unidade</t>
+          <t>permuta_financeira[1].unidade</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="D610" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_valor</t>
+          <t>permuta_financeira[1].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="D611" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_valor</t>
+          <t>permuta_financeira[1].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="D612" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].permuta_financeira_deduzir_imposto</t>
+          <t>permuta_financeira[1].deduzir_imposto</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="D613" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].permuta_financeira_deduzir_corretagem</t>
+          <t>permuta_financeira[1].deduzir_corretagem</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="D614" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_unidade</t>
+          <t>permuta_financeira[2].unidade</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="D615" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_valor</t>
+          <t>permuta_financeira[2].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="D616" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_valor</t>
+          <t>permuta_financeira[2].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="D617" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].permuta_financeira_deduzir_imposto</t>
+          <t>permuta_financeira[2].deduzir_imposto</t>
         </is>
       </c>
     </row>
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D618" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].permuta_financeira_deduzir_corretagem</t>
+          <t>permuta_financeira[2].deduzir_corretagem</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D621" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].nome</t>
+          <t>funding.financiamento_producao.nome</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="D622" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].ativo</t>
+          <t>funding.financiamento_producao.ativo</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="D623" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].valor</t>
+          <t>funding.financiamento_producao.valor</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="D624" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].taxa_anual</t>
+          <t>funding.financiamento_producao.taxa_anual</t>
         </is>
       </c>
     </row>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="D625" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].exposicao_minima</t>
+          <t>funding.financiamento_producao.exposicao_minima</t>
         </is>
       </c>
     </row>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="D626" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].percentual_financiavel</t>
+          <t>funding.financiamento_producao.percentual_financiavel</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="D627" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].amortizar_com_caixa_disponivel</t>
+          <t>funding.financiamento_producao.amortizar_com_caixa_disponivel</t>
         </is>
       </c>
     </row>
@@ -10927,12 +10927,12 @@
       <c r="B628" s="6" t="n"/>
       <c r="C628" s="7" t="inlineStr">
         <is>
-          <t>linhas de custo (texto); vazio = padrão</t>
+          <t>linhas de custo separadas por ";" — Categoria ou Categoria / Subcategoria; vazio = padrão</t>
         </is>
       </c>
       <c r="D628" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].custo_linha_ids</t>
+          <t>funding.financiamento_producao.base_financiavel</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="D630" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].nome</t>
+          <t>funding.divida[1].nome</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="D631" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].valor</t>
+          <t>funding.divida[1].valor</t>
         </is>
       </c>
     </row>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="D632" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[1].aporte</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D633" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].inicio_mes</t>
+          <t>funding.divida[1].mes</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="D634" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].distribuir_aporte</t>
+          <t>funding.divida[1].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="D635" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].aporte_meses</t>
+          <t>funding.divida[1].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="D636" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_anual</t>
+          <t>funding.divida[1].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="D637" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].periodo_amortizacao_meses</t>
+          <t>funding.divida[1].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="D638" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].periodo_carencia_meses</t>
+          <t>funding.divida[1].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D639" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_estruturacao_pct</t>
+          <t>funding.divida[1].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="D640" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_administracao_mensal</t>
+          <t>funding.divida[1].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="D641" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].outros_encargos_iniciais</t>
+          <t>funding.divida[1].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="D643" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].nome</t>
+          <t>funding.divida[2].nome</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="D644" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].valor</t>
+          <t>funding.divida[2].valor</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="D645" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[2].aporte</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="D646" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].inicio_mes</t>
+          <t>funding.divida[2].mes</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="D647" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].distribuir_aporte</t>
+          <t>funding.divida[2].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="D648" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].aporte_meses</t>
+          <t>funding.divida[2].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="D649" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_anual</t>
+          <t>funding.divida[2].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="D650" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].periodo_amortizacao_meses</t>
+          <t>funding.divida[2].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D651" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].periodo_carencia_meses</t>
+          <t>funding.divida[2].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="D652" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_estruturacao_pct</t>
+          <t>funding.divida[2].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="D653" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_administracao_mensal</t>
+          <t>funding.divida[2].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="D654" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].outros_encargos_iniciais</t>
+          <t>funding.divida[2].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="D656" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].nome</t>
+          <t>funding.divida[3].nome</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="D657" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].valor</t>
+          <t>funding.divida[3].valor</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="D658" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[3].aporte</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="D659" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].inicio_mes</t>
+          <t>funding.divida[3].mes</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="D660" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].distribuir_aporte</t>
+          <t>funding.divida[3].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="D661" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].aporte_meses</t>
+          <t>funding.divida[3].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="D662" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_anual</t>
+          <t>funding.divida[3].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="D663" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].periodo_amortizacao_meses</t>
+          <t>funding.divida[3].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="D664" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].periodo_carencia_meses</t>
+          <t>funding.divida[3].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="D665" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_estruturacao_pct</t>
+          <t>funding.divida[3].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="D666" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_administracao_mensal</t>
+          <t>funding.divida[3].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="D667" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].outros_encargos_iniciais</t>
+          <t>funding.divida[3].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D669" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].nome</t>
+          <t>funding.equity[1].nome</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
       </c>
       <c r="D670" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].valor</t>
+          <t>funding.equity[1].valor</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="D671" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[1].aporte</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="D672" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].inicio_mes</t>
+          <t>funding.equity[1].mes</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="D673" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].modo_retorno</t>
+          <t>funding.equity[1].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="D674" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].pct_retorno</t>
+          <t>funding.equity[1].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="D676" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].nome</t>
+          <t>funding.equity[2].nome</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="D677" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].valor</t>
+          <t>funding.equity[2].valor</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="D678" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[2].aporte</t>
         </is>
       </c>
     </row>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="D679" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].inicio_mes</t>
+          <t>funding.equity[2].mes</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="D680" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].modo_retorno</t>
+          <t>funding.equity[2].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="D681" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].pct_retorno</t>
+          <t>funding.equity[2].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="D683" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].nome</t>
+          <t>funding.equity[3].nome</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="D684" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].valor</t>
+          <t>funding.equity[3].valor</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="D685" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[3].aporte</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D686" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].inicio_mes</t>
+          <t>funding.equity[3].mes</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="D687" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].modo_retorno</t>
+          <t>funding.equity[3].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="D688" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].pct_retorno</t>
+          <t>funding.equity[3].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="D690" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].nome</t>
+          <t>cenarios[1].nome</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="D691" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].preco_venda_pct</t>
+          <t>cenarios[1].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="D692" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].custo_obra_pct</t>
+          <t>cenarios[1].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="D693" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].nome</t>
+          <t>cenarios[2].nome</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="D694" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].preco_venda_pct</t>
+          <t>cenarios[2].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="D695" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].custo_obra_pct</t>
+          <t>cenarios[2].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="D696" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].nome</t>
+          <t>cenarios[3].nome</t>
         </is>
       </c>
     </row>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="D697" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].preco_venda_pct</t>
+          <t>cenarios[3].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="D698" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].custo_obra_pct</t>
+          <t>cenarios[3].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="D699" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].nome</t>
+          <t>cenarios[4].nome</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="D700" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].preco_venda_pct</t>
+          <t>cenarios[4].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="D701" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].custo_obra_pct</t>
+          <t>cenarios[4].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="D702" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].nome</t>
+          <t>cenarios[5].nome</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12205,7 @@
       </c>
       <c r="D703" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].preco_venda_pct</t>
+          <t>cenarios[5].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="D704" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].custo_obra_pct</t>
+          <t>cenarios[5].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -15051,16 +15051,16 @@
     <row r="844">
       <c r="A844" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — terreno</t>
-        </is>
-      </c>
-      <c r="B844" s="24">
-        <f>IF($B$296="terreno",N($B$816),0)+IF($B$307="terreno",N($B$817),0)+IF($B$318="terreno",N($B$818),0)+IF($B$329="terreno",N($B$819),0)+IF($B$340="terreno",N($B$820),0)+IF($B$351="terreno",N($B$821),0)+IF($B$362="terreno",N($B$822),0)+IF($B$373="terreno",N($B$823),0)+IF($B$384="terreno",N($B$824),0)+IF($B$395="terreno",N($B$825),0)+IF($B$406="terreno",N($B$826),0)+IF($B$417="terreno",N($B$827),0)+IF($B$428="terreno",N($B$828),0)+IF($B$439="terreno",N($B$829),0)+IF($B$450="terreno",N($B$830),0)+IF($B$461="terreno",N($B$831),0)+IF($B$472="terreno",N($B$832),0)+IF($B$483="terreno",N($B$833),0)+IF($B$494="terreno",N($B$834),0)+IF($B$505="terreno",N($B$835),0)+IF($B$516="terreno",N($B$836),0)+IF($B$527="terreno",N($B$837),0)+IF($B$538="terreno",N($B$838),0)+IF($B$549="terreno",N($B$839),0)+IF($B$560="terreno",N($B$840),0)+IF($B$571="terreno",N($B$841),0)+IF($B$582="terreno",N($B$842),0)+IF($B$593="terreno",N($B$843),0)</f>
+          <t>Custo 1 — conferência</t>
+        </is>
+      </c>
+      <c r="B844" s="23">
+        <f>IF(AND($B$296="",$B$297=""),"",IF(OR($B$296="",$B$297="",$B$299=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$296="terreno",$B$297="Preço",OR($B$299="rs",$B$299="rs_m2_terreno")),AND($B$296="terreno",$B$297="Registro",OR($B$299="rs",$B$299="rs_m2_priv")),AND($B$296="terreno",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="obra",$B$297="Construção",OR($B$299="rs",$B$299="rs_m2_priv")),AND($B$296="obra",$B$297="Outorga",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="obra",$B$297="Decoração",OR($B$299="rs",$B$299="rs_m2_priv")),AND($B$296="obra",$B$297="Gestão da obra",OR($B$299="rs",$B$299="pct_obra")),AND($B$296="obra",$B$297="Contingência",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="obra",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="diretos",$B$297="Marketing &amp; Publicidade",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="diretos",$B$297="Corretagem de vendas",OR($B$299="pct_vgv")),AND($B$296="diretos",$B$297="Projetos",OR($B$299="rs",$B$299="rs_m2_priv",$B$299="pct_constr")),AND($B$296="diretos",$B$297="Licenças e Aprovações",OR($B$299="rs",$B$299="rs_m2_priv")),AND($B$296="diretos",$B$297="Manutenção pós-obra",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="diretos",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="indireto",$B$297="Marketing global",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="indireto",$B$297="Stand de vendas",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="indireto",$B$297="Gestão",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="indireto",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="financeiro",$B$297="Juros de financiamento",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="financeiro",$B$297="Taxas bancárias",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="financeiro",$B$297="Estruturação de dívida",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="financeiro",$B$297="Investidores",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="financeiro",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$300&lt;&gt;"",$B$301&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$299,3)="pct",$B$301="",$B$300=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C844" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D844" s="21" t="inlineStr">
@@ -15072,16 +15072,16 @@
     <row r="845">
       <c r="A845" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — obra</t>
-        </is>
-      </c>
-      <c r="B845" s="24">
-        <f>IF($B$296="obra",N($B$816),0)+IF($B$307="obra",N($B$817),0)+IF($B$318="obra",N($B$818),0)+IF($B$329="obra",N($B$819),0)+IF($B$340="obra",N($B$820),0)+IF($B$351="obra",N($B$821),0)+IF($B$362="obra",N($B$822),0)+IF($B$373="obra",N($B$823),0)+IF($B$384="obra",N($B$824),0)+IF($B$395="obra",N($B$825),0)+IF($B$406="obra",N($B$826),0)+IF($B$417="obra",N($B$827),0)+IF($B$428="obra",N($B$828),0)+IF($B$439="obra",N($B$829),0)+IF($B$450="obra",N($B$830),0)+IF($B$461="obra",N($B$831),0)+IF($B$472="obra",N($B$832),0)+IF($B$483="obra",N($B$833),0)+IF($B$494="obra",N($B$834),0)+IF($B$505="obra",N($B$835),0)+IF($B$516="obra",N($B$836),0)+IF($B$527="obra",N($B$837),0)+IF($B$538="obra",N($B$838),0)+IF($B$549="obra",N($B$839),0)+IF($B$560="obra",N($B$840),0)+IF($B$571="obra",N($B$841),0)+IF($B$582="obra",N($B$842),0)+IF($B$593="obra",N($B$843),0)</f>
+          <t>Custo 2 — conferência</t>
+        </is>
+      </c>
+      <c r="B845" s="23">
+        <f>IF(AND($B$307="",$B$308=""),"",IF(OR($B$307="",$B$308="",$B$310=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$307="terreno",$B$308="Preço",OR($B$310="rs",$B$310="rs_m2_terreno")),AND($B$307="terreno",$B$308="Registro",OR($B$310="rs",$B$310="rs_m2_priv")),AND($B$307="terreno",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="obra",$B$308="Construção",OR($B$310="rs",$B$310="rs_m2_priv")),AND($B$307="obra",$B$308="Outorga",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="obra",$B$308="Decoração",OR($B$310="rs",$B$310="rs_m2_priv")),AND($B$307="obra",$B$308="Gestão da obra",OR($B$310="rs",$B$310="pct_obra")),AND($B$307="obra",$B$308="Contingência",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="obra",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="diretos",$B$308="Marketing &amp; Publicidade",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="diretos",$B$308="Corretagem de vendas",OR($B$310="pct_vgv")),AND($B$307="diretos",$B$308="Projetos",OR($B$310="rs",$B$310="rs_m2_priv",$B$310="pct_constr")),AND($B$307="diretos",$B$308="Licenças e Aprovações",OR($B$310="rs",$B$310="rs_m2_priv")),AND($B$307="diretos",$B$308="Manutenção pós-obra",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="diretos",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="indireto",$B$308="Marketing global",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="indireto",$B$308="Stand de vendas",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="indireto",$B$308="Gestão",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="indireto",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="financeiro",$B$308="Juros de financiamento",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="financeiro",$B$308="Taxas bancárias",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="financeiro",$B$308="Estruturação de dívida",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="financeiro",$B$308="Investidores",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="financeiro",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$311&lt;&gt;"",$B$312&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$310,3)="pct",$B$312="",$B$311=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C845" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D845" s="21" t="inlineStr">
@@ -15093,16 +15093,16 @@
     <row r="846">
       <c r="A846" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — diretos</t>
-        </is>
-      </c>
-      <c r="B846" s="24">
-        <f>IF($B$296="diretos",N($B$816),0)+IF($B$307="diretos",N($B$817),0)+IF($B$318="diretos",N($B$818),0)+IF($B$329="diretos",N($B$819),0)+IF($B$340="diretos",N($B$820),0)+IF($B$351="diretos",N($B$821),0)+IF($B$362="diretos",N($B$822),0)+IF($B$373="diretos",N($B$823),0)+IF($B$384="diretos",N($B$824),0)+IF($B$395="diretos",N($B$825),0)+IF($B$406="diretos",N($B$826),0)+IF($B$417="diretos",N($B$827),0)+IF($B$428="diretos",N($B$828),0)+IF($B$439="diretos",N($B$829),0)+IF($B$450="diretos",N($B$830),0)+IF($B$461="diretos",N($B$831),0)+IF($B$472="diretos",N($B$832),0)+IF($B$483="diretos",N($B$833),0)+IF($B$494="diretos",N($B$834),0)+IF($B$505="diretos",N($B$835),0)+IF($B$516="diretos",N($B$836),0)+IF($B$527="diretos",N($B$837),0)+IF($B$538="diretos",N($B$838),0)+IF($B$549="diretos",N($B$839),0)+IF($B$560="diretos",N($B$840),0)+IF($B$571="diretos",N($B$841),0)+IF($B$582="diretos",N($B$842),0)+IF($B$593="diretos",N($B$843),0)</f>
+          <t>Custo 3 — conferência</t>
+        </is>
+      </c>
+      <c r="B846" s="23">
+        <f>IF(AND($B$318="",$B$319=""),"",IF(OR($B$318="",$B$319="",$B$321=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$318="terreno",$B$319="Preço",OR($B$321="rs",$B$321="rs_m2_terreno")),AND($B$318="terreno",$B$319="Registro",OR($B$321="rs",$B$321="rs_m2_priv")),AND($B$318="terreno",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="obra",$B$319="Construção",OR($B$321="rs",$B$321="rs_m2_priv")),AND($B$318="obra",$B$319="Outorga",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="obra",$B$319="Decoração",OR($B$321="rs",$B$321="rs_m2_priv")),AND($B$318="obra",$B$319="Gestão da obra",OR($B$321="rs",$B$321="pct_obra")),AND($B$318="obra",$B$319="Contingência",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="obra",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="diretos",$B$319="Marketing &amp; Publicidade",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="diretos",$B$319="Corretagem de vendas",OR($B$321="pct_vgv")),AND($B$318="diretos",$B$319="Projetos",OR($B$321="rs",$B$321="rs_m2_priv",$B$321="pct_constr")),AND($B$318="diretos",$B$319="Licenças e Aprovações",OR($B$321="rs",$B$321="rs_m2_priv")),AND($B$318="diretos",$B$319="Manutenção pós-obra",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="diretos",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="indireto",$B$319="Marketing global",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="indireto",$B$319="Stand de vendas",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="indireto",$B$319="Gestão",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="indireto",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="financeiro",$B$319="Juros de financiamento",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="financeiro",$B$319="Taxas bancárias",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="financeiro",$B$319="Estruturação de dívida",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="financeiro",$B$319="Investidores",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="financeiro",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$322&lt;&gt;"",$B$323&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$321,3)="pct",$B$323="",$B$322=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C846" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D846" s="21" t="inlineStr">
@@ -15114,16 +15114,16 @@
     <row r="847">
       <c r="A847" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — indireto</t>
-        </is>
-      </c>
-      <c r="B847" s="24">
-        <f>IF($B$296="indireto",N($B$816),0)+IF($B$307="indireto",N($B$817),0)+IF($B$318="indireto",N($B$818),0)+IF($B$329="indireto",N($B$819),0)+IF($B$340="indireto",N($B$820),0)+IF($B$351="indireto",N($B$821),0)+IF($B$362="indireto",N($B$822),0)+IF($B$373="indireto",N($B$823),0)+IF($B$384="indireto",N($B$824),0)+IF($B$395="indireto",N($B$825),0)+IF($B$406="indireto",N($B$826),0)+IF($B$417="indireto",N($B$827),0)+IF($B$428="indireto",N($B$828),0)+IF($B$439="indireto",N($B$829),0)+IF($B$450="indireto",N($B$830),0)+IF($B$461="indireto",N($B$831),0)+IF($B$472="indireto",N($B$832),0)+IF($B$483="indireto",N($B$833),0)+IF($B$494="indireto",N($B$834),0)+IF($B$505="indireto",N($B$835),0)+IF($B$516="indireto",N($B$836),0)+IF($B$527="indireto",N($B$837),0)+IF($B$538="indireto",N($B$838),0)+IF($B$549="indireto",N($B$839),0)+IF($B$560="indireto",N($B$840),0)+IF($B$571="indireto",N($B$841),0)+IF($B$582="indireto",N($B$842),0)+IF($B$593="indireto",N($B$843),0)</f>
+          <t>Custo 4 — conferência</t>
+        </is>
+      </c>
+      <c r="B847" s="23">
+        <f>IF(AND($B$329="",$B$330=""),"",IF(OR($B$329="",$B$330="",$B$332=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$329="terreno",$B$330="Preço",OR($B$332="rs",$B$332="rs_m2_terreno")),AND($B$329="terreno",$B$330="Registro",OR($B$332="rs",$B$332="rs_m2_priv")),AND($B$329="terreno",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="obra",$B$330="Construção",OR($B$332="rs",$B$332="rs_m2_priv")),AND($B$329="obra",$B$330="Outorga",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="obra",$B$330="Decoração",OR($B$332="rs",$B$332="rs_m2_priv")),AND($B$329="obra",$B$330="Gestão da obra",OR($B$332="rs",$B$332="pct_obra")),AND($B$329="obra",$B$330="Contingência",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="obra",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="diretos",$B$330="Marketing &amp; Publicidade",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="diretos",$B$330="Corretagem de vendas",OR($B$332="pct_vgv")),AND($B$329="diretos",$B$330="Projetos",OR($B$332="rs",$B$332="rs_m2_priv",$B$332="pct_constr")),AND($B$329="diretos",$B$330="Licenças e Aprovações",OR($B$332="rs",$B$332="rs_m2_priv")),AND($B$329="diretos",$B$330="Manutenção pós-obra",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="diretos",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="indireto",$B$330="Marketing global",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="indireto",$B$330="Stand de vendas",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="indireto",$B$330="Gestão",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="indireto",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="financeiro",$B$330="Juros de financiamento",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="financeiro",$B$330="Taxas bancárias",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="financeiro",$B$330="Estruturação de dívida",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="financeiro",$B$330="Investidores",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="financeiro",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$333&lt;&gt;"",$B$334&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$332,3)="pct",$B$334="",$B$333=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C847" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D847" s="21" t="inlineStr">
@@ -15135,16 +15135,16 @@
     <row r="848">
       <c r="A848" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — financeiro</t>
-        </is>
-      </c>
-      <c r="B848" s="24">
-        <f>IF($B$296="financeiro",N($B$816),0)+IF($B$307="financeiro",N($B$817),0)+IF($B$318="financeiro",N($B$818),0)+IF($B$329="financeiro",N($B$819),0)+IF($B$340="financeiro",N($B$820),0)+IF($B$351="financeiro",N($B$821),0)+IF($B$362="financeiro",N($B$822),0)+IF($B$373="financeiro",N($B$823),0)+IF($B$384="financeiro",N($B$824),0)+IF($B$395="financeiro",N($B$825),0)+IF($B$406="financeiro",N($B$826),0)+IF($B$417="financeiro",N($B$827),0)+IF($B$428="financeiro",N($B$828),0)+IF($B$439="financeiro",N($B$829),0)+IF($B$450="financeiro",N($B$830),0)+IF($B$461="financeiro",N($B$831),0)+IF($B$472="financeiro",N($B$832),0)+IF($B$483="financeiro",N($B$833),0)+IF($B$494="financeiro",N($B$834),0)+IF($B$505="financeiro",N($B$835),0)+IF($B$516="financeiro",N($B$836),0)+IF($B$527="financeiro",N($B$837),0)+IF($B$538="financeiro",N($B$838),0)+IF($B$549="financeiro",N($B$839),0)+IF($B$560="financeiro",N($B$840),0)+IF($B$571="financeiro",N($B$841),0)+IF($B$582="financeiro",N($B$842),0)+IF($B$593="financeiro",N($B$843),0)</f>
+          <t>Custo 5 — conferência</t>
+        </is>
+      </c>
+      <c r="B848" s="23">
+        <f>IF(AND($B$340="",$B$341=""),"",IF(OR($B$340="",$B$341="",$B$343=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$340="terreno",$B$341="Preço",OR($B$343="rs",$B$343="rs_m2_terreno")),AND($B$340="terreno",$B$341="Registro",OR($B$343="rs",$B$343="rs_m2_priv")),AND($B$340="terreno",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="obra",$B$341="Construção",OR($B$343="rs",$B$343="rs_m2_priv")),AND($B$340="obra",$B$341="Outorga",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="obra",$B$341="Decoração",OR($B$343="rs",$B$343="rs_m2_priv")),AND($B$340="obra",$B$341="Gestão da obra",OR($B$343="rs",$B$343="pct_obra")),AND($B$340="obra",$B$341="Contingência",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="obra",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="diretos",$B$341="Marketing &amp; Publicidade",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="diretos",$B$341="Corretagem de vendas",OR($B$343="pct_vgv")),AND($B$340="diretos",$B$341="Projetos",OR($B$343="rs",$B$343="rs_m2_priv",$B$343="pct_constr")),AND($B$340="diretos",$B$341="Licenças e Aprovações",OR($B$343="rs",$B$343="rs_m2_priv")),AND($B$340="diretos",$B$341="Manutenção pós-obra",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="diretos",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="indireto",$B$341="Marketing global",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="indireto",$B$341="Stand de vendas",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="indireto",$B$341="Gestão",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="indireto",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="financeiro",$B$341="Juros de financiamento",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="financeiro",$B$341="Taxas bancárias",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="financeiro",$B$341="Estruturação de dívida",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="financeiro",$B$341="Investidores",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="financeiro",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$344&lt;&gt;"",$B$345&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$343,3)="pct",$B$345="",$B$344=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C848" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D848" s="21" t="inlineStr">
@@ -15156,16 +15156,16 @@
     <row r="849">
       <c r="A849" s="18" t="inlineStr">
         <is>
-          <t>Permuta física 1 — VGV entregue (unidades × área × preço sugerido)</t>
-        </is>
-      </c>
-      <c r="B849" s="24">
-        <f>IF($B$604="",0,N($B$605)*(($B$58=$B$604)*(N($B$59)+N($B$60))*N($B$62)+($B$64=$B$604)*(N($B$65)+N($B$66))*N($B$68)+($B$70=$B$604)*(N($B$71)+N($B$72))*N($B$74)+($B$76=$B$604)*(N($B$77)+N($B$78))*N($B$80)+($B$82=$B$604)*(N($B$83)+N($B$84))*N($B$86)+($B$88=$B$604)*(N($B$89)+N($B$90))*N($B$92)+($B$94=$B$604)*(N($B$95)+N($B$96))*N($B$98)+($B$100=$B$604)*(N($B$101)+N($B$102))*N($B$104)+($B$106=$B$604)*(N($B$107)+N($B$108))*N($B$110)+($B$112=$B$604)*(N($B$113)+N($B$114))*N($B$116)))</f>
+          <t>Custo 6 — conferência</t>
+        </is>
+      </c>
+      <c r="B849" s="23">
+        <f>IF(AND($B$351="",$B$352=""),"",IF(OR($B$351="",$B$352="",$B$354=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$351="terreno",$B$352="Preço",OR($B$354="rs",$B$354="rs_m2_terreno")),AND($B$351="terreno",$B$352="Registro",OR($B$354="rs",$B$354="rs_m2_priv")),AND($B$351="terreno",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="obra",$B$352="Construção",OR($B$354="rs",$B$354="rs_m2_priv")),AND($B$351="obra",$B$352="Outorga",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="obra",$B$352="Decoração",OR($B$354="rs",$B$354="rs_m2_priv")),AND($B$351="obra",$B$352="Gestão da obra",OR($B$354="rs",$B$354="pct_obra")),AND($B$351="obra",$B$352="Contingência",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="obra",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="diretos",$B$352="Marketing &amp; Publicidade",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="diretos",$B$352="Corretagem de vendas",OR($B$354="pct_vgv")),AND($B$351="diretos",$B$352="Projetos",OR($B$354="rs",$B$354="rs_m2_priv",$B$354="pct_constr")),AND($B$351="diretos",$B$352="Licenças e Aprovações",OR($B$354="rs",$B$354="rs_m2_priv")),AND($B$351="diretos",$B$352="Manutenção pós-obra",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="diretos",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="indireto",$B$352="Marketing global",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="indireto",$B$352="Stand de vendas",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="indireto",$B$352="Gestão",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="indireto",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="financeiro",$B$352="Juros de financiamento",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="financeiro",$B$352="Taxas bancárias",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="financeiro",$B$352="Estruturação de dívida",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="financeiro",$B$352="Investidores",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="financeiro",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$355&lt;&gt;"",$B$356&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$354,3)="pct",$B$356="",$B$355=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C849" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D849" s="21" t="inlineStr">
@@ -15177,16 +15177,16 @@
     <row r="850">
       <c r="A850" s="18" t="inlineStr">
         <is>
-          <t>Permuta financeira 1 — equivalente em R$</t>
-        </is>
-      </c>
-      <c r="B850" s="24">
-        <f>IF($B$609="pct_vgv",N($B$611)*$B$757,IF($B$609="rs",N($B$610),0))</f>
+          <t>Custo 7 — conferência</t>
+        </is>
+      </c>
+      <c r="B850" s="23">
+        <f>IF(AND($B$362="",$B$363=""),"",IF(OR($B$362="",$B$363="",$B$365=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$362="terreno",$B$363="Preço",OR($B$365="rs",$B$365="rs_m2_terreno")),AND($B$362="terreno",$B$363="Registro",OR($B$365="rs",$B$365="rs_m2_priv")),AND($B$362="terreno",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="obra",$B$363="Construção",OR($B$365="rs",$B$365="rs_m2_priv")),AND($B$362="obra",$B$363="Outorga",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="obra",$B$363="Decoração",OR($B$365="rs",$B$365="rs_m2_priv")),AND($B$362="obra",$B$363="Gestão da obra",OR($B$365="rs",$B$365="pct_obra")),AND($B$362="obra",$B$363="Contingência",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="obra",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="diretos",$B$363="Marketing &amp; Publicidade",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="diretos",$B$363="Corretagem de vendas",OR($B$365="pct_vgv")),AND($B$362="diretos",$B$363="Projetos",OR($B$365="rs",$B$365="rs_m2_priv",$B$365="pct_constr")),AND($B$362="diretos",$B$363="Licenças e Aprovações",OR($B$365="rs",$B$365="rs_m2_priv")),AND($B$362="diretos",$B$363="Manutenção pós-obra",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="diretos",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="indireto",$B$363="Marketing global",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="indireto",$B$363="Stand de vendas",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="indireto",$B$363="Gestão",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="indireto",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="financeiro",$B$363="Juros de financiamento",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="financeiro",$B$363="Taxas bancárias",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="financeiro",$B$363="Estruturação de dívida",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="financeiro",$B$363="Investidores",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="financeiro",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$366&lt;&gt;"",$B$367&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$365,3)="pct",$B$367="",$B$366=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C850" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D850" s="21" t="inlineStr">
@@ -15198,16 +15198,16 @@
     <row r="851">
       <c r="A851" s="18" t="inlineStr">
         <is>
-          <t>Permuta física 2 — VGV entregue (unidades × área × preço sugerido)</t>
-        </is>
-      </c>
-      <c r="B851" s="24">
-        <f>IF($B$606="",0,N($B$607)*(($B$58=$B$606)*(N($B$59)+N($B$60))*N($B$62)+($B$64=$B$606)*(N($B$65)+N($B$66))*N($B$68)+($B$70=$B$606)*(N($B$71)+N($B$72))*N($B$74)+($B$76=$B$606)*(N($B$77)+N($B$78))*N($B$80)+($B$82=$B$606)*(N($B$83)+N($B$84))*N($B$86)+($B$88=$B$606)*(N($B$89)+N($B$90))*N($B$92)+($B$94=$B$606)*(N($B$95)+N($B$96))*N($B$98)+($B$100=$B$606)*(N($B$101)+N($B$102))*N($B$104)+($B$106=$B$606)*(N($B$107)+N($B$108))*N($B$110)+($B$112=$B$606)*(N($B$113)+N($B$114))*N($B$116)))</f>
+          <t>Custo 8 — conferência</t>
+        </is>
+      </c>
+      <c r="B851" s="23">
+        <f>IF(AND($B$373="",$B$374=""),"",IF(OR($B$373="",$B$374="",$B$376=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$373="terreno",$B$374="Preço",OR($B$376="rs",$B$376="rs_m2_terreno")),AND($B$373="terreno",$B$374="Registro",OR($B$376="rs",$B$376="rs_m2_priv")),AND($B$373="terreno",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="obra",$B$374="Construção",OR($B$376="rs",$B$376="rs_m2_priv")),AND($B$373="obra",$B$374="Outorga",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="obra",$B$374="Decoração",OR($B$376="rs",$B$376="rs_m2_priv")),AND($B$373="obra",$B$374="Gestão da obra",OR($B$376="rs",$B$376="pct_obra")),AND($B$373="obra",$B$374="Contingência",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="obra",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="diretos",$B$374="Marketing &amp; Publicidade",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="diretos",$B$374="Corretagem de vendas",OR($B$376="pct_vgv")),AND($B$373="diretos",$B$374="Projetos",OR($B$376="rs",$B$376="rs_m2_priv",$B$376="pct_constr")),AND($B$373="diretos",$B$374="Licenças e Aprovações",OR($B$376="rs",$B$376="rs_m2_priv")),AND($B$373="diretos",$B$374="Manutenção pós-obra",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="diretos",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="indireto",$B$374="Marketing global",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="indireto",$B$374="Stand de vendas",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="indireto",$B$374="Gestão",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="indireto",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="financeiro",$B$374="Juros de financiamento",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="financeiro",$B$374="Taxas bancárias",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="financeiro",$B$374="Estruturação de dívida",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="financeiro",$B$374="Investidores",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="financeiro",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$377&lt;&gt;"",$B$378&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$376,3)="pct",$B$378="",$B$377=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C851" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D851" s="21" t="inlineStr">
@@ -15219,16 +15219,16 @@
     <row r="852">
       <c r="A852" s="18" t="inlineStr">
         <is>
-          <t>Permuta financeira 2 — equivalente em R$</t>
-        </is>
-      </c>
-      <c r="B852" s="24">
-        <f>IF($B$614="pct_vgv",N($B$616)*$B$757,IF($B$614="rs",N($B$615),0))</f>
+          <t>Custo 9 — conferência</t>
+        </is>
+      </c>
+      <c r="B852" s="23">
+        <f>IF(AND($B$384="",$B$385=""),"",IF(OR($B$384="",$B$385="",$B$387=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$384="terreno",$B$385="Preço",OR($B$387="rs",$B$387="rs_m2_terreno")),AND($B$384="terreno",$B$385="Registro",OR($B$387="rs",$B$387="rs_m2_priv")),AND($B$384="terreno",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="obra",$B$385="Construção",OR($B$387="rs",$B$387="rs_m2_priv")),AND($B$384="obra",$B$385="Outorga",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="obra",$B$385="Decoração",OR($B$387="rs",$B$387="rs_m2_priv")),AND($B$384="obra",$B$385="Gestão da obra",OR($B$387="rs",$B$387="pct_obra")),AND($B$384="obra",$B$385="Contingência",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="obra",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="diretos",$B$385="Marketing &amp; Publicidade",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="diretos",$B$385="Corretagem de vendas",OR($B$387="pct_vgv")),AND($B$384="diretos",$B$385="Projetos",OR($B$387="rs",$B$387="rs_m2_priv",$B$387="pct_constr")),AND($B$384="diretos",$B$385="Licenças e Aprovações",OR($B$387="rs",$B$387="rs_m2_priv")),AND($B$384="diretos",$B$385="Manutenção pós-obra",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="diretos",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="indireto",$B$385="Marketing global",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="indireto",$B$385="Stand de vendas",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="indireto",$B$385="Gestão",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="indireto",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="financeiro",$B$385="Juros de financiamento",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="financeiro",$B$385="Taxas bancárias",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="financeiro",$B$385="Estruturação de dívida",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="financeiro",$B$385="Investidores",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="financeiro",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$388&lt;&gt;"",$B$389&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$387,3)="pct",$B$389="",$B$388=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C852" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D852" s="21" t="inlineStr">
@@ -15240,16 +15240,16 @@
     <row r="853">
       <c r="A853" s="18" t="inlineStr">
         <is>
-          <t>Σ valor das dívidas</t>
-        </is>
-      </c>
-      <c r="B853" s="24">
-        <f>N($B$631)+N($B$644)+N($B$657)</f>
+          <t>Custo 10 — conferência</t>
+        </is>
+      </c>
+      <c r="B853" s="23">
+        <f>IF(AND($B$395="",$B$396=""),"",IF(OR($B$395="",$B$396="",$B$398=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$395="terreno",$B$396="Preço",OR($B$398="rs",$B$398="rs_m2_terreno")),AND($B$395="terreno",$B$396="Registro",OR($B$398="rs",$B$398="rs_m2_priv")),AND($B$395="terreno",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="obra",$B$396="Construção",OR($B$398="rs",$B$398="rs_m2_priv")),AND($B$395="obra",$B$396="Outorga",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="obra",$B$396="Decoração",OR($B$398="rs",$B$398="rs_m2_priv")),AND($B$395="obra",$B$396="Gestão da obra",OR($B$398="rs",$B$398="pct_obra")),AND($B$395="obra",$B$396="Contingência",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="obra",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="diretos",$B$396="Marketing &amp; Publicidade",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="diretos",$B$396="Corretagem de vendas",OR($B$398="pct_vgv")),AND($B$395="diretos",$B$396="Projetos",OR($B$398="rs",$B$398="rs_m2_priv",$B$398="pct_constr")),AND($B$395="diretos",$B$396="Licenças e Aprovações",OR($B$398="rs",$B$398="rs_m2_priv")),AND($B$395="diretos",$B$396="Manutenção pós-obra",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="diretos",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="indireto",$B$396="Marketing global",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="indireto",$B$396="Stand de vendas",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="indireto",$B$396="Gestão",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="indireto",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="financeiro",$B$396="Juros de financiamento",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="financeiro",$B$396="Taxas bancárias",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="financeiro",$B$396="Estruturação de dívida",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="financeiro",$B$396="Investidores",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="financeiro",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$399&lt;&gt;"",$B$400&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$398,3)="pct",$B$400="",$B$399=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C853" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D853" s="21" t="inlineStr">
@@ -15261,203 +15261,840 @@
     <row r="854">
       <c r="A854" s="18" t="inlineStr">
         <is>
+          <t>Custo 11 — conferência</t>
+        </is>
+      </c>
+      <c r="B854" s="23">
+        <f>IF(AND($B$406="",$B$407=""),"",IF(OR($B$406="",$B$407="",$B$409=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$406="terreno",$B$407="Preço",OR($B$409="rs",$B$409="rs_m2_terreno")),AND($B$406="terreno",$B$407="Registro",OR($B$409="rs",$B$409="rs_m2_priv")),AND($B$406="terreno",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="obra",$B$407="Construção",OR($B$409="rs",$B$409="rs_m2_priv")),AND($B$406="obra",$B$407="Outorga",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="obra",$B$407="Decoração",OR($B$409="rs",$B$409="rs_m2_priv")),AND($B$406="obra",$B$407="Gestão da obra",OR($B$409="rs",$B$409="pct_obra")),AND($B$406="obra",$B$407="Contingência",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="obra",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="diretos",$B$407="Marketing &amp; Publicidade",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="diretos",$B$407="Corretagem de vendas",OR($B$409="pct_vgv")),AND($B$406="diretos",$B$407="Projetos",OR($B$409="rs",$B$409="rs_m2_priv",$B$409="pct_constr")),AND($B$406="diretos",$B$407="Licenças e Aprovações",OR($B$409="rs",$B$409="rs_m2_priv")),AND($B$406="diretos",$B$407="Manutenção pós-obra",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="diretos",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="indireto",$B$407="Marketing global",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="indireto",$B$407="Stand de vendas",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="indireto",$B$407="Gestão",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="indireto",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="financeiro",$B$407="Juros de financiamento",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="financeiro",$B$407="Taxas bancárias",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="financeiro",$B$407="Estruturação de dívida",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="financeiro",$B$407="Investidores",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="financeiro",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$410&lt;&gt;"",$B$411&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$409,3)="pct",$B$411="",$B$410=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C854" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D854" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="18" t="inlineStr">
+        <is>
+          <t>Custo 12 — conferência</t>
+        </is>
+      </c>
+      <c r="B855" s="23">
+        <f>IF(AND($B$417="",$B$418=""),"",IF(OR($B$417="",$B$418="",$B$420=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$417="terreno",$B$418="Preço",OR($B$420="rs",$B$420="rs_m2_terreno")),AND($B$417="terreno",$B$418="Registro",OR($B$420="rs",$B$420="rs_m2_priv")),AND($B$417="terreno",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="obra",$B$418="Construção",OR($B$420="rs",$B$420="rs_m2_priv")),AND($B$417="obra",$B$418="Outorga",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="obra",$B$418="Decoração",OR($B$420="rs",$B$420="rs_m2_priv")),AND($B$417="obra",$B$418="Gestão da obra",OR($B$420="rs",$B$420="pct_obra")),AND($B$417="obra",$B$418="Contingência",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="obra",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="diretos",$B$418="Marketing &amp; Publicidade",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="diretos",$B$418="Corretagem de vendas",OR($B$420="pct_vgv")),AND($B$417="diretos",$B$418="Projetos",OR($B$420="rs",$B$420="rs_m2_priv",$B$420="pct_constr")),AND($B$417="diretos",$B$418="Licenças e Aprovações",OR($B$420="rs",$B$420="rs_m2_priv")),AND($B$417="diretos",$B$418="Manutenção pós-obra",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="diretos",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="indireto",$B$418="Marketing global",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="indireto",$B$418="Stand de vendas",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="indireto",$B$418="Gestão",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="indireto",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="financeiro",$B$418="Juros de financiamento",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="financeiro",$B$418="Taxas bancárias",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="financeiro",$B$418="Estruturação de dívida",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="financeiro",$B$418="Investidores",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="financeiro",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$421&lt;&gt;"",$B$422&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$420,3)="pct",$B$422="",$B$421=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C855" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D855" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="18" t="inlineStr">
+        <is>
+          <t>Custo 13 — conferência</t>
+        </is>
+      </c>
+      <c r="B856" s="23">
+        <f>IF(AND($B$428="",$B$429=""),"",IF(OR($B$428="",$B$429="",$B$431=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$428="terreno",$B$429="Preço",OR($B$431="rs",$B$431="rs_m2_terreno")),AND($B$428="terreno",$B$429="Registro",OR($B$431="rs",$B$431="rs_m2_priv")),AND($B$428="terreno",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="obra",$B$429="Construção",OR($B$431="rs",$B$431="rs_m2_priv")),AND($B$428="obra",$B$429="Outorga",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="obra",$B$429="Decoração",OR($B$431="rs",$B$431="rs_m2_priv")),AND($B$428="obra",$B$429="Gestão da obra",OR($B$431="rs",$B$431="pct_obra")),AND($B$428="obra",$B$429="Contingência",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="obra",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="diretos",$B$429="Marketing &amp; Publicidade",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="diretos",$B$429="Corretagem de vendas",OR($B$431="pct_vgv")),AND($B$428="diretos",$B$429="Projetos",OR($B$431="rs",$B$431="rs_m2_priv",$B$431="pct_constr")),AND($B$428="diretos",$B$429="Licenças e Aprovações",OR($B$431="rs",$B$431="rs_m2_priv")),AND($B$428="diretos",$B$429="Manutenção pós-obra",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="diretos",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="indireto",$B$429="Marketing global",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="indireto",$B$429="Stand de vendas",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="indireto",$B$429="Gestão",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="indireto",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="financeiro",$B$429="Juros de financiamento",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="financeiro",$B$429="Taxas bancárias",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="financeiro",$B$429="Estruturação de dívida",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="financeiro",$B$429="Investidores",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="financeiro",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$432&lt;&gt;"",$B$433&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$431,3)="pct",$B$433="",$B$432=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C856" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D856" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="18" t="inlineStr">
+        <is>
+          <t>Custo 14 — conferência</t>
+        </is>
+      </c>
+      <c r="B857" s="23">
+        <f>IF(AND($B$439="",$B$440=""),"",IF(OR($B$439="",$B$440="",$B$442=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$439="terreno",$B$440="Preço",OR($B$442="rs",$B$442="rs_m2_terreno")),AND($B$439="terreno",$B$440="Registro",OR($B$442="rs",$B$442="rs_m2_priv")),AND($B$439="terreno",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="obra",$B$440="Construção",OR($B$442="rs",$B$442="rs_m2_priv")),AND($B$439="obra",$B$440="Outorga",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="obra",$B$440="Decoração",OR($B$442="rs",$B$442="rs_m2_priv")),AND($B$439="obra",$B$440="Gestão da obra",OR($B$442="rs",$B$442="pct_obra")),AND($B$439="obra",$B$440="Contingência",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="obra",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="diretos",$B$440="Marketing &amp; Publicidade",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="diretos",$B$440="Corretagem de vendas",OR($B$442="pct_vgv")),AND($B$439="diretos",$B$440="Projetos",OR($B$442="rs",$B$442="rs_m2_priv",$B$442="pct_constr")),AND($B$439="diretos",$B$440="Licenças e Aprovações",OR($B$442="rs",$B$442="rs_m2_priv")),AND($B$439="diretos",$B$440="Manutenção pós-obra",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="diretos",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="indireto",$B$440="Marketing global",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="indireto",$B$440="Stand de vendas",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="indireto",$B$440="Gestão",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="indireto",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="financeiro",$B$440="Juros de financiamento",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="financeiro",$B$440="Taxas bancárias",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="financeiro",$B$440="Estruturação de dívida",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="financeiro",$B$440="Investidores",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="financeiro",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$443&lt;&gt;"",$B$444&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$442,3)="pct",$B$444="",$B$443=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C857" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D857" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="18" t="inlineStr">
+        <is>
+          <t>Custo 15 — conferência</t>
+        </is>
+      </c>
+      <c r="B858" s="23">
+        <f>IF(AND($B$450="",$B$451=""),"",IF(OR($B$450="",$B$451="",$B$453=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$450="terreno",$B$451="Preço",OR($B$453="rs",$B$453="rs_m2_terreno")),AND($B$450="terreno",$B$451="Registro",OR($B$453="rs",$B$453="rs_m2_priv")),AND($B$450="terreno",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="obra",$B$451="Construção",OR($B$453="rs",$B$453="rs_m2_priv")),AND($B$450="obra",$B$451="Outorga",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="obra",$B$451="Decoração",OR($B$453="rs",$B$453="rs_m2_priv")),AND($B$450="obra",$B$451="Gestão da obra",OR($B$453="rs",$B$453="pct_obra")),AND($B$450="obra",$B$451="Contingência",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="obra",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="diretos",$B$451="Marketing &amp; Publicidade",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="diretos",$B$451="Corretagem de vendas",OR($B$453="pct_vgv")),AND($B$450="diretos",$B$451="Projetos",OR($B$453="rs",$B$453="rs_m2_priv",$B$453="pct_constr")),AND($B$450="diretos",$B$451="Licenças e Aprovações",OR($B$453="rs",$B$453="rs_m2_priv")),AND($B$450="diretos",$B$451="Manutenção pós-obra",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="diretos",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="indireto",$B$451="Marketing global",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="indireto",$B$451="Stand de vendas",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="indireto",$B$451="Gestão",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="indireto",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="financeiro",$B$451="Juros de financiamento",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="financeiro",$B$451="Taxas bancárias",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="financeiro",$B$451="Estruturação de dívida",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="financeiro",$B$451="Investidores",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="financeiro",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$454&lt;&gt;"",$B$455&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$453,3)="pct",$B$455="",$B$454=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C858" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D858" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="18" t="inlineStr">
+        <is>
+          <t>Custo 16 — conferência</t>
+        </is>
+      </c>
+      <c r="B859" s="23">
+        <f>IF(AND($B$461="",$B$462=""),"",IF(OR($B$461="",$B$462="",$B$464=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$461="terreno",$B$462="Preço",OR($B$464="rs",$B$464="rs_m2_terreno")),AND($B$461="terreno",$B$462="Registro",OR($B$464="rs",$B$464="rs_m2_priv")),AND($B$461="terreno",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="obra",$B$462="Construção",OR($B$464="rs",$B$464="rs_m2_priv")),AND($B$461="obra",$B$462="Outorga",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="obra",$B$462="Decoração",OR($B$464="rs",$B$464="rs_m2_priv")),AND($B$461="obra",$B$462="Gestão da obra",OR($B$464="rs",$B$464="pct_obra")),AND($B$461="obra",$B$462="Contingência",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="obra",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="diretos",$B$462="Marketing &amp; Publicidade",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="diretos",$B$462="Corretagem de vendas",OR($B$464="pct_vgv")),AND($B$461="diretos",$B$462="Projetos",OR($B$464="rs",$B$464="rs_m2_priv",$B$464="pct_constr")),AND($B$461="diretos",$B$462="Licenças e Aprovações",OR($B$464="rs",$B$464="rs_m2_priv")),AND($B$461="diretos",$B$462="Manutenção pós-obra",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="diretos",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="indireto",$B$462="Marketing global",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="indireto",$B$462="Stand de vendas",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="indireto",$B$462="Gestão",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="indireto",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="financeiro",$B$462="Juros de financiamento",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="financeiro",$B$462="Taxas bancárias",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="financeiro",$B$462="Estruturação de dívida",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="financeiro",$B$462="Investidores",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="financeiro",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$465&lt;&gt;"",$B$466&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$464,3)="pct",$B$466="",$B$465=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C859" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D859" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="18" t="inlineStr">
+        <is>
+          <t>Custo 17 — conferência</t>
+        </is>
+      </c>
+      <c r="B860" s="23">
+        <f>IF(AND($B$472="",$B$473=""),"",IF(OR($B$472="",$B$473="",$B$475=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$472="terreno",$B$473="Preço",OR($B$475="rs",$B$475="rs_m2_terreno")),AND($B$472="terreno",$B$473="Registro",OR($B$475="rs",$B$475="rs_m2_priv")),AND($B$472="terreno",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="obra",$B$473="Construção",OR($B$475="rs",$B$475="rs_m2_priv")),AND($B$472="obra",$B$473="Outorga",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="obra",$B$473="Decoração",OR($B$475="rs",$B$475="rs_m2_priv")),AND($B$472="obra",$B$473="Gestão da obra",OR($B$475="rs",$B$475="pct_obra")),AND($B$472="obra",$B$473="Contingência",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="obra",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="diretos",$B$473="Marketing &amp; Publicidade",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="diretos",$B$473="Corretagem de vendas",OR($B$475="pct_vgv")),AND($B$472="diretos",$B$473="Projetos",OR($B$475="rs",$B$475="rs_m2_priv",$B$475="pct_constr")),AND($B$472="diretos",$B$473="Licenças e Aprovações",OR($B$475="rs",$B$475="rs_m2_priv")),AND($B$472="diretos",$B$473="Manutenção pós-obra",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="diretos",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="indireto",$B$473="Marketing global",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="indireto",$B$473="Stand de vendas",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="indireto",$B$473="Gestão",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="indireto",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="financeiro",$B$473="Juros de financiamento",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="financeiro",$B$473="Taxas bancárias",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="financeiro",$B$473="Estruturação de dívida",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="financeiro",$B$473="Investidores",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="financeiro",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$476&lt;&gt;"",$B$477&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$475,3)="pct",$B$477="",$B$476=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C860" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D860" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="18" t="inlineStr">
+        <is>
+          <t>Custo 18 — conferência</t>
+        </is>
+      </c>
+      <c r="B861" s="23">
+        <f>IF(AND($B$483="",$B$484=""),"",IF(OR($B$483="",$B$484="",$B$486=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$483="terreno",$B$484="Preço",OR($B$486="rs",$B$486="rs_m2_terreno")),AND($B$483="terreno",$B$484="Registro",OR($B$486="rs",$B$486="rs_m2_priv")),AND($B$483="terreno",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="obra",$B$484="Construção",OR($B$486="rs",$B$486="rs_m2_priv")),AND($B$483="obra",$B$484="Outorga",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="obra",$B$484="Decoração",OR($B$486="rs",$B$486="rs_m2_priv")),AND($B$483="obra",$B$484="Gestão da obra",OR($B$486="rs",$B$486="pct_obra")),AND($B$483="obra",$B$484="Contingência",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="obra",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="diretos",$B$484="Marketing &amp; Publicidade",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="diretos",$B$484="Corretagem de vendas",OR($B$486="pct_vgv")),AND($B$483="diretos",$B$484="Projetos",OR($B$486="rs",$B$486="rs_m2_priv",$B$486="pct_constr")),AND($B$483="diretos",$B$484="Licenças e Aprovações",OR($B$486="rs",$B$486="rs_m2_priv")),AND($B$483="diretos",$B$484="Manutenção pós-obra",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="diretos",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="indireto",$B$484="Marketing global",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="indireto",$B$484="Stand de vendas",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="indireto",$B$484="Gestão",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="indireto",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="financeiro",$B$484="Juros de financiamento",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="financeiro",$B$484="Taxas bancárias",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="financeiro",$B$484="Estruturação de dívida",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="financeiro",$B$484="Investidores",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="financeiro",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$487&lt;&gt;"",$B$488&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$486,3)="pct",$B$488="",$B$487=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C861" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D861" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="18" t="inlineStr">
+        <is>
+          <t>Custo 19 — conferência</t>
+        </is>
+      </c>
+      <c r="B862" s="23">
+        <f>IF(AND($B$494="",$B$495=""),"",IF(OR($B$494="",$B$495="",$B$497=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$494="terreno",$B$495="Preço",OR($B$497="rs",$B$497="rs_m2_terreno")),AND($B$494="terreno",$B$495="Registro",OR($B$497="rs",$B$497="rs_m2_priv")),AND($B$494="terreno",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="obra",$B$495="Construção",OR($B$497="rs",$B$497="rs_m2_priv")),AND($B$494="obra",$B$495="Outorga",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="obra",$B$495="Decoração",OR($B$497="rs",$B$497="rs_m2_priv")),AND($B$494="obra",$B$495="Gestão da obra",OR($B$497="rs",$B$497="pct_obra")),AND($B$494="obra",$B$495="Contingência",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="obra",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="diretos",$B$495="Marketing &amp; Publicidade",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="diretos",$B$495="Corretagem de vendas",OR($B$497="pct_vgv")),AND($B$494="diretos",$B$495="Projetos",OR($B$497="rs",$B$497="rs_m2_priv",$B$497="pct_constr")),AND($B$494="diretos",$B$495="Licenças e Aprovações",OR($B$497="rs",$B$497="rs_m2_priv")),AND($B$494="diretos",$B$495="Manutenção pós-obra",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="diretos",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="indireto",$B$495="Marketing global",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="indireto",$B$495="Stand de vendas",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="indireto",$B$495="Gestão",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="indireto",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="financeiro",$B$495="Juros de financiamento",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="financeiro",$B$495="Taxas bancárias",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="financeiro",$B$495="Estruturação de dívida",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="financeiro",$B$495="Investidores",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="financeiro",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$498&lt;&gt;"",$B$499&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$497,3)="pct",$B$499="",$B$498=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C862" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D862" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="18" t="inlineStr">
+        <is>
+          <t>Custo 20 — conferência</t>
+        </is>
+      </c>
+      <c r="B863" s="23">
+        <f>IF(AND($B$505="",$B$506=""),"",IF(OR($B$505="",$B$506="",$B$508=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$505="terreno",$B$506="Preço",OR($B$508="rs",$B$508="rs_m2_terreno")),AND($B$505="terreno",$B$506="Registro",OR($B$508="rs",$B$508="rs_m2_priv")),AND($B$505="terreno",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="obra",$B$506="Construção",OR($B$508="rs",$B$508="rs_m2_priv")),AND($B$505="obra",$B$506="Outorga",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="obra",$B$506="Decoração",OR($B$508="rs",$B$508="rs_m2_priv")),AND($B$505="obra",$B$506="Gestão da obra",OR($B$508="rs",$B$508="pct_obra")),AND($B$505="obra",$B$506="Contingência",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="obra",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="diretos",$B$506="Marketing &amp; Publicidade",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="diretos",$B$506="Corretagem de vendas",OR($B$508="pct_vgv")),AND($B$505="diretos",$B$506="Projetos",OR($B$508="rs",$B$508="rs_m2_priv",$B$508="pct_constr")),AND($B$505="diretos",$B$506="Licenças e Aprovações",OR($B$508="rs",$B$508="rs_m2_priv")),AND($B$505="diretos",$B$506="Manutenção pós-obra",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="diretos",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="indireto",$B$506="Marketing global",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="indireto",$B$506="Stand de vendas",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="indireto",$B$506="Gestão",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="indireto",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="financeiro",$B$506="Juros de financiamento",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="financeiro",$B$506="Taxas bancárias",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="financeiro",$B$506="Estruturação de dívida",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="financeiro",$B$506="Investidores",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="financeiro",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$509&lt;&gt;"",$B$510&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$508,3)="pct",$B$510="",$B$509=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C863" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D863" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="18" t="inlineStr">
+        <is>
+          <t>Custo 21 — conferência</t>
+        </is>
+      </c>
+      <c r="B864" s="23">
+        <f>IF(AND($B$516="",$B$517=""),"",IF(OR($B$516="",$B$517="",$B$519=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$516="terreno",$B$517="Preço",OR($B$519="rs",$B$519="rs_m2_terreno")),AND($B$516="terreno",$B$517="Registro",OR($B$519="rs",$B$519="rs_m2_priv")),AND($B$516="terreno",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="obra",$B$517="Construção",OR($B$519="rs",$B$519="rs_m2_priv")),AND($B$516="obra",$B$517="Outorga",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="obra",$B$517="Decoração",OR($B$519="rs",$B$519="rs_m2_priv")),AND($B$516="obra",$B$517="Gestão da obra",OR($B$519="rs",$B$519="pct_obra")),AND($B$516="obra",$B$517="Contingência",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="obra",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="diretos",$B$517="Marketing &amp; Publicidade",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="diretos",$B$517="Corretagem de vendas",OR($B$519="pct_vgv")),AND($B$516="diretos",$B$517="Projetos",OR($B$519="rs",$B$519="rs_m2_priv",$B$519="pct_constr")),AND($B$516="diretos",$B$517="Licenças e Aprovações",OR($B$519="rs",$B$519="rs_m2_priv")),AND($B$516="diretos",$B$517="Manutenção pós-obra",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="diretos",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="indireto",$B$517="Marketing global",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="indireto",$B$517="Stand de vendas",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="indireto",$B$517="Gestão",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="indireto",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="financeiro",$B$517="Juros de financiamento",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="financeiro",$B$517="Taxas bancárias",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="financeiro",$B$517="Estruturação de dívida",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="financeiro",$B$517="Investidores",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="financeiro",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$520&lt;&gt;"",$B$521&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$519,3)="pct",$B$521="",$B$520=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C864" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D864" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="18" t="inlineStr">
+        <is>
+          <t>Custo 22 — conferência</t>
+        </is>
+      </c>
+      <c r="B865" s="23">
+        <f>IF(AND($B$527="",$B$528=""),"",IF(OR($B$527="",$B$528="",$B$530=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$527="terreno",$B$528="Preço",OR($B$530="rs",$B$530="rs_m2_terreno")),AND($B$527="terreno",$B$528="Registro",OR($B$530="rs",$B$530="rs_m2_priv")),AND($B$527="terreno",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="obra",$B$528="Construção",OR($B$530="rs",$B$530="rs_m2_priv")),AND($B$527="obra",$B$528="Outorga",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="obra",$B$528="Decoração",OR($B$530="rs",$B$530="rs_m2_priv")),AND($B$527="obra",$B$528="Gestão da obra",OR($B$530="rs",$B$530="pct_obra")),AND($B$527="obra",$B$528="Contingência",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="obra",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="diretos",$B$528="Marketing &amp; Publicidade",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="diretos",$B$528="Corretagem de vendas",OR($B$530="pct_vgv")),AND($B$527="diretos",$B$528="Projetos",OR($B$530="rs",$B$530="rs_m2_priv",$B$530="pct_constr")),AND($B$527="diretos",$B$528="Licenças e Aprovações",OR($B$530="rs",$B$530="rs_m2_priv")),AND($B$527="diretos",$B$528="Manutenção pós-obra",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="diretos",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="indireto",$B$528="Marketing global",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="indireto",$B$528="Stand de vendas",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="indireto",$B$528="Gestão",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="indireto",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="financeiro",$B$528="Juros de financiamento",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="financeiro",$B$528="Taxas bancárias",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="financeiro",$B$528="Estruturação de dívida",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="financeiro",$B$528="Investidores",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="financeiro",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$531&lt;&gt;"",$B$532&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$530,3)="pct",$B$532="",$B$531=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C865" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D865" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="18" t="inlineStr">
+        <is>
+          <t>Custo 23 — conferência</t>
+        </is>
+      </c>
+      <c r="B866" s="23">
+        <f>IF(AND($B$538="",$B$539=""),"",IF(OR($B$538="",$B$539="",$B$541=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$538="terreno",$B$539="Preço",OR($B$541="rs",$B$541="rs_m2_terreno")),AND($B$538="terreno",$B$539="Registro",OR($B$541="rs",$B$541="rs_m2_priv")),AND($B$538="terreno",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="obra",$B$539="Construção",OR($B$541="rs",$B$541="rs_m2_priv")),AND($B$538="obra",$B$539="Outorga",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="obra",$B$539="Decoração",OR($B$541="rs",$B$541="rs_m2_priv")),AND($B$538="obra",$B$539="Gestão da obra",OR($B$541="rs",$B$541="pct_obra")),AND($B$538="obra",$B$539="Contingência",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="obra",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="diretos",$B$539="Marketing &amp; Publicidade",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="diretos",$B$539="Corretagem de vendas",OR($B$541="pct_vgv")),AND($B$538="diretos",$B$539="Projetos",OR($B$541="rs",$B$541="rs_m2_priv",$B$541="pct_constr")),AND($B$538="diretos",$B$539="Licenças e Aprovações",OR($B$541="rs",$B$541="rs_m2_priv")),AND($B$538="diretos",$B$539="Manutenção pós-obra",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="diretos",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="indireto",$B$539="Marketing global",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="indireto",$B$539="Stand de vendas",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="indireto",$B$539="Gestão",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="indireto",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="financeiro",$B$539="Juros de financiamento",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="financeiro",$B$539="Taxas bancárias",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="financeiro",$B$539="Estruturação de dívida",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="financeiro",$B$539="Investidores",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="financeiro",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$542&lt;&gt;"",$B$543&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$541,3)="pct",$B$543="",$B$542=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C866" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D866" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="18" t="inlineStr">
+        <is>
+          <t>Custo 24 — conferência</t>
+        </is>
+      </c>
+      <c r="B867" s="23">
+        <f>IF(AND($B$549="",$B$550=""),"",IF(OR($B$549="",$B$550="",$B$552=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$549="terreno",$B$550="Preço",OR($B$552="rs",$B$552="rs_m2_terreno")),AND($B$549="terreno",$B$550="Registro",OR($B$552="rs",$B$552="rs_m2_priv")),AND($B$549="terreno",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="obra",$B$550="Construção",OR($B$552="rs",$B$552="rs_m2_priv")),AND($B$549="obra",$B$550="Outorga",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="obra",$B$550="Decoração",OR($B$552="rs",$B$552="rs_m2_priv")),AND($B$549="obra",$B$550="Gestão da obra",OR($B$552="rs",$B$552="pct_obra")),AND($B$549="obra",$B$550="Contingência",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="obra",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="diretos",$B$550="Marketing &amp; Publicidade",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="diretos",$B$550="Corretagem de vendas",OR($B$552="pct_vgv")),AND($B$549="diretos",$B$550="Projetos",OR($B$552="rs",$B$552="rs_m2_priv",$B$552="pct_constr")),AND($B$549="diretos",$B$550="Licenças e Aprovações",OR($B$552="rs",$B$552="rs_m2_priv")),AND($B$549="diretos",$B$550="Manutenção pós-obra",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="diretos",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="indireto",$B$550="Marketing global",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="indireto",$B$550="Stand de vendas",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="indireto",$B$550="Gestão",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="indireto",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="financeiro",$B$550="Juros de financiamento",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="financeiro",$B$550="Taxas bancárias",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="financeiro",$B$550="Estruturação de dívida",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="financeiro",$B$550="Investidores",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="financeiro",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$553&lt;&gt;"",$B$554&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$552,3)="pct",$B$554="",$B$553=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C867" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D867" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="18" t="inlineStr">
+        <is>
+          <t>Custo 25 — conferência</t>
+        </is>
+      </c>
+      <c r="B868" s="23">
+        <f>IF(AND($B$560="",$B$561=""),"",IF(OR($B$560="",$B$561="",$B$563=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$560="terreno",$B$561="Preço",OR($B$563="rs",$B$563="rs_m2_terreno")),AND($B$560="terreno",$B$561="Registro",OR($B$563="rs",$B$563="rs_m2_priv")),AND($B$560="terreno",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="obra",$B$561="Construção",OR($B$563="rs",$B$563="rs_m2_priv")),AND($B$560="obra",$B$561="Outorga",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="obra",$B$561="Decoração",OR($B$563="rs",$B$563="rs_m2_priv")),AND($B$560="obra",$B$561="Gestão da obra",OR($B$563="rs",$B$563="pct_obra")),AND($B$560="obra",$B$561="Contingência",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="obra",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="diretos",$B$561="Marketing &amp; Publicidade",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="diretos",$B$561="Corretagem de vendas",OR($B$563="pct_vgv")),AND($B$560="diretos",$B$561="Projetos",OR($B$563="rs",$B$563="rs_m2_priv",$B$563="pct_constr")),AND($B$560="diretos",$B$561="Licenças e Aprovações",OR($B$563="rs",$B$563="rs_m2_priv")),AND($B$560="diretos",$B$561="Manutenção pós-obra",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="diretos",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="indireto",$B$561="Marketing global",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="indireto",$B$561="Stand de vendas",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="indireto",$B$561="Gestão",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="indireto",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="financeiro",$B$561="Juros de financiamento",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="financeiro",$B$561="Taxas bancárias",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="financeiro",$B$561="Estruturação de dívida",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="financeiro",$B$561="Investidores",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="financeiro",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$564&lt;&gt;"",$B$565&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$563,3)="pct",$B$565="",$B$564=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C868" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D868" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="18" t="inlineStr">
+        <is>
+          <t>Custo 26 — conferência</t>
+        </is>
+      </c>
+      <c r="B869" s="23">
+        <f>IF(AND($B$571="",$B$572=""),"",IF(OR($B$571="",$B$572="",$B$574=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$571="terreno",$B$572="Preço",OR($B$574="rs",$B$574="rs_m2_terreno")),AND($B$571="terreno",$B$572="Registro",OR($B$574="rs",$B$574="rs_m2_priv")),AND($B$571="terreno",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="obra",$B$572="Construção",OR($B$574="rs",$B$574="rs_m2_priv")),AND($B$571="obra",$B$572="Outorga",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="obra",$B$572="Decoração",OR($B$574="rs",$B$574="rs_m2_priv")),AND($B$571="obra",$B$572="Gestão da obra",OR($B$574="rs",$B$574="pct_obra")),AND($B$571="obra",$B$572="Contingência",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="obra",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="diretos",$B$572="Marketing &amp; Publicidade",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="diretos",$B$572="Corretagem de vendas",OR($B$574="pct_vgv")),AND($B$571="diretos",$B$572="Projetos",OR($B$574="rs",$B$574="rs_m2_priv",$B$574="pct_constr")),AND($B$571="diretos",$B$572="Licenças e Aprovações",OR($B$574="rs",$B$574="rs_m2_priv")),AND($B$571="diretos",$B$572="Manutenção pós-obra",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="diretos",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="indireto",$B$572="Marketing global",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="indireto",$B$572="Stand de vendas",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="indireto",$B$572="Gestão",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="indireto",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="financeiro",$B$572="Juros de financiamento",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="financeiro",$B$572="Taxas bancárias",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="financeiro",$B$572="Estruturação de dívida",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="financeiro",$B$572="Investidores",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="financeiro",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$575&lt;&gt;"",$B$576&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$574,3)="pct",$B$576="",$B$575=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C869" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D869" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="18" t="inlineStr">
+        <is>
+          <t>Custo 27 — conferência</t>
+        </is>
+      </c>
+      <c r="B870" s="23">
+        <f>IF(AND($B$582="",$B$583=""),"",IF(OR($B$582="",$B$583="",$B$585=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$582="terreno",$B$583="Preço",OR($B$585="rs",$B$585="rs_m2_terreno")),AND($B$582="terreno",$B$583="Registro",OR($B$585="rs",$B$585="rs_m2_priv")),AND($B$582="terreno",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="obra",$B$583="Construção",OR($B$585="rs",$B$585="rs_m2_priv")),AND($B$582="obra",$B$583="Outorga",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="obra",$B$583="Decoração",OR($B$585="rs",$B$585="rs_m2_priv")),AND($B$582="obra",$B$583="Gestão da obra",OR($B$585="rs",$B$585="pct_obra")),AND($B$582="obra",$B$583="Contingência",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="obra",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="diretos",$B$583="Marketing &amp; Publicidade",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="diretos",$B$583="Corretagem de vendas",OR($B$585="pct_vgv")),AND($B$582="diretos",$B$583="Projetos",OR($B$585="rs",$B$585="rs_m2_priv",$B$585="pct_constr")),AND($B$582="diretos",$B$583="Licenças e Aprovações",OR($B$585="rs",$B$585="rs_m2_priv")),AND($B$582="diretos",$B$583="Manutenção pós-obra",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="diretos",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="indireto",$B$583="Marketing global",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="indireto",$B$583="Stand de vendas",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="indireto",$B$583="Gestão",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="indireto",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="financeiro",$B$583="Juros de financiamento",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="financeiro",$B$583="Taxas bancárias",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="financeiro",$B$583="Estruturação de dívida",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="financeiro",$B$583="Investidores",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="financeiro",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$586&lt;&gt;"",$B$587&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$585,3)="pct",$B$587="",$B$586=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C870" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D870" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="18" t="inlineStr">
+        <is>
+          <t>Custo 28 — conferência</t>
+        </is>
+      </c>
+      <c r="B871" s="23">
+        <f>IF(AND($B$593="",$B$594=""),"",IF(OR($B$593="",$B$594="",$B$596=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$593="terreno",$B$594="Preço",OR($B$596="rs",$B$596="rs_m2_terreno")),AND($B$593="terreno",$B$594="Registro",OR($B$596="rs",$B$596="rs_m2_priv")),AND($B$593="terreno",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="obra",$B$594="Construção",OR($B$596="rs",$B$596="rs_m2_priv")),AND($B$593="obra",$B$594="Outorga",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="obra",$B$594="Decoração",OR($B$596="rs",$B$596="rs_m2_priv")),AND($B$593="obra",$B$594="Gestão da obra",OR($B$596="rs",$B$596="pct_obra")),AND($B$593="obra",$B$594="Contingência",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="obra",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="diretos",$B$594="Marketing &amp; Publicidade",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="diretos",$B$594="Corretagem de vendas",OR($B$596="pct_vgv")),AND($B$593="diretos",$B$594="Projetos",OR($B$596="rs",$B$596="rs_m2_priv",$B$596="pct_constr")),AND($B$593="diretos",$B$594="Licenças e Aprovações",OR($B$596="rs",$B$596="rs_m2_priv")),AND($B$593="diretos",$B$594="Manutenção pós-obra",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="diretos",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="indireto",$B$594="Marketing global",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="indireto",$B$594="Stand de vendas",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="indireto",$B$594="Gestão",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="indireto",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="financeiro",$B$594="Juros de financiamento",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="financeiro",$B$594="Taxas bancárias",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="financeiro",$B$594="Estruturação de dívida",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="financeiro",$B$594="Investidores",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="financeiro",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$597&lt;&gt;"",$B$598&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$596,3)="pct",$B$598="",$B$597=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C871" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D871" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="18" t="inlineStr">
+        <is>
+          <t>Cada 1% do VGV de tabela equivale a (para converter Projetos, que não aceita % do VGV)</t>
+        </is>
+      </c>
+      <c r="B872" s="24">
+        <f>$B$757*0.01</f>
+        <v/>
+      </c>
+      <c r="C872" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D872" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — terreno</t>
+        </is>
+      </c>
+      <c r="B873" s="24">
+        <f>IF($B$296="terreno",N($B$816),0)+IF($B$307="terreno",N($B$817),0)+IF($B$318="terreno",N($B$818),0)+IF($B$329="terreno",N($B$819),0)+IF($B$340="terreno",N($B$820),0)+IF($B$351="terreno",N($B$821),0)+IF($B$362="terreno",N($B$822),0)+IF($B$373="terreno",N($B$823),0)+IF($B$384="terreno",N($B$824),0)+IF($B$395="terreno",N($B$825),0)+IF($B$406="terreno",N($B$826),0)+IF($B$417="terreno",N($B$827),0)+IF($B$428="terreno",N($B$828),0)+IF($B$439="terreno",N($B$829),0)+IF($B$450="terreno",N($B$830),0)+IF($B$461="terreno",N($B$831),0)+IF($B$472="terreno",N($B$832),0)+IF($B$483="terreno",N($B$833),0)+IF($B$494="terreno",N($B$834),0)+IF($B$505="terreno",N($B$835),0)+IF($B$516="terreno",N($B$836),0)+IF($B$527="terreno",N($B$837),0)+IF($B$538="terreno",N($B$838),0)+IF($B$549="terreno",N($B$839),0)+IF($B$560="terreno",N($B$840),0)+IF($B$571="terreno",N($B$841),0)+IF($B$582="terreno",N($B$842),0)+IF($B$593="terreno",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C873" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D873" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — obra</t>
+        </is>
+      </c>
+      <c r="B874" s="24">
+        <f>IF($B$296="obra",N($B$816),0)+IF($B$307="obra",N($B$817),0)+IF($B$318="obra",N($B$818),0)+IF($B$329="obra",N($B$819),0)+IF($B$340="obra",N($B$820),0)+IF($B$351="obra",N($B$821),0)+IF($B$362="obra",N($B$822),0)+IF($B$373="obra",N($B$823),0)+IF($B$384="obra",N($B$824),0)+IF($B$395="obra",N($B$825),0)+IF($B$406="obra",N($B$826),0)+IF($B$417="obra",N($B$827),0)+IF($B$428="obra",N($B$828),0)+IF($B$439="obra",N($B$829),0)+IF($B$450="obra",N($B$830),0)+IF($B$461="obra",N($B$831),0)+IF($B$472="obra",N($B$832),0)+IF($B$483="obra",N($B$833),0)+IF($B$494="obra",N($B$834),0)+IF($B$505="obra",N($B$835),0)+IF($B$516="obra",N($B$836),0)+IF($B$527="obra",N($B$837),0)+IF($B$538="obra",N($B$838),0)+IF($B$549="obra",N($B$839),0)+IF($B$560="obra",N($B$840),0)+IF($B$571="obra",N($B$841),0)+IF($B$582="obra",N($B$842),0)+IF($B$593="obra",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C874" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D874" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — diretos</t>
+        </is>
+      </c>
+      <c r="B875" s="24">
+        <f>IF($B$296="diretos",N($B$816),0)+IF($B$307="diretos",N($B$817),0)+IF($B$318="diretos",N($B$818),0)+IF($B$329="diretos",N($B$819),0)+IF($B$340="diretos",N($B$820),0)+IF($B$351="diretos",N($B$821),0)+IF($B$362="diretos",N($B$822),0)+IF($B$373="diretos",N($B$823),0)+IF($B$384="diretos",N($B$824),0)+IF($B$395="diretos",N($B$825),0)+IF($B$406="diretos",N($B$826),0)+IF($B$417="diretos",N($B$827),0)+IF($B$428="diretos",N($B$828),0)+IF($B$439="diretos",N($B$829),0)+IF($B$450="diretos",N($B$830),0)+IF($B$461="diretos",N($B$831),0)+IF($B$472="diretos",N($B$832),0)+IF($B$483="diretos",N($B$833),0)+IF($B$494="diretos",N($B$834),0)+IF($B$505="diretos",N($B$835),0)+IF($B$516="diretos",N($B$836),0)+IF($B$527="diretos",N($B$837),0)+IF($B$538="diretos",N($B$838),0)+IF($B$549="diretos",N($B$839),0)+IF($B$560="diretos",N($B$840),0)+IF($B$571="diretos",N($B$841),0)+IF($B$582="diretos",N($B$842),0)+IF($B$593="diretos",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C875" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D875" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — indireto</t>
+        </is>
+      </c>
+      <c r="B876" s="24">
+        <f>IF($B$296="indireto",N($B$816),0)+IF($B$307="indireto",N($B$817),0)+IF($B$318="indireto",N($B$818),0)+IF($B$329="indireto",N($B$819),0)+IF($B$340="indireto",N($B$820),0)+IF($B$351="indireto",N($B$821),0)+IF($B$362="indireto",N($B$822),0)+IF($B$373="indireto",N($B$823),0)+IF($B$384="indireto",N($B$824),0)+IF($B$395="indireto",N($B$825),0)+IF($B$406="indireto",N($B$826),0)+IF($B$417="indireto",N($B$827),0)+IF($B$428="indireto",N($B$828),0)+IF($B$439="indireto",N($B$829),0)+IF($B$450="indireto",N($B$830),0)+IF($B$461="indireto",N($B$831),0)+IF($B$472="indireto",N($B$832),0)+IF($B$483="indireto",N($B$833),0)+IF($B$494="indireto",N($B$834),0)+IF($B$505="indireto",N($B$835),0)+IF($B$516="indireto",N($B$836),0)+IF($B$527="indireto",N($B$837),0)+IF($B$538="indireto",N($B$838),0)+IF($B$549="indireto",N($B$839),0)+IF($B$560="indireto",N($B$840),0)+IF($B$571="indireto",N($B$841),0)+IF($B$582="indireto",N($B$842),0)+IF($B$593="indireto",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C876" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D876" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — financeiro</t>
+        </is>
+      </c>
+      <c r="B877" s="24">
+        <f>IF($B$296="financeiro",N($B$816),0)+IF($B$307="financeiro",N($B$817),0)+IF($B$318="financeiro",N($B$818),0)+IF($B$329="financeiro",N($B$819),0)+IF($B$340="financeiro",N($B$820),0)+IF($B$351="financeiro",N($B$821),0)+IF($B$362="financeiro",N($B$822),0)+IF($B$373="financeiro",N($B$823),0)+IF($B$384="financeiro",N($B$824),0)+IF($B$395="financeiro",N($B$825),0)+IF($B$406="financeiro",N($B$826),0)+IF($B$417="financeiro",N($B$827),0)+IF($B$428="financeiro",N($B$828),0)+IF($B$439="financeiro",N($B$829),0)+IF($B$450="financeiro",N($B$830),0)+IF($B$461="financeiro",N($B$831),0)+IF($B$472="financeiro",N($B$832),0)+IF($B$483="financeiro",N($B$833),0)+IF($B$494="financeiro",N($B$834),0)+IF($B$505="financeiro",N($B$835),0)+IF($B$516="financeiro",N($B$836),0)+IF($B$527="financeiro",N($B$837),0)+IF($B$538="financeiro",N($B$838),0)+IF($B$549="financeiro",N($B$839),0)+IF($B$560="financeiro",N($B$840),0)+IF($B$571="financeiro",N($B$841),0)+IF($B$582="financeiro",N($B$842),0)+IF($B$593="financeiro",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C877" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D877" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="18" t="inlineStr">
+        <is>
+          <t>Permuta física 1 — VGV entregue (unidades × área × preço sugerido)</t>
+        </is>
+      </c>
+      <c r="B878" s="24">
+        <f>IF($B$604="",0,N($B$605)*(($B$58=$B$604)*(N($B$59)+N($B$60))*N($B$62)+($B$64=$B$604)*(N($B$65)+N($B$66))*N($B$68)+($B$70=$B$604)*(N($B$71)+N($B$72))*N($B$74)+($B$76=$B$604)*(N($B$77)+N($B$78))*N($B$80)+($B$82=$B$604)*(N($B$83)+N($B$84))*N($B$86)+($B$88=$B$604)*(N($B$89)+N($B$90))*N($B$92)+($B$94=$B$604)*(N($B$95)+N($B$96))*N($B$98)+($B$100=$B$604)*(N($B$101)+N($B$102))*N($B$104)+($B$106=$B$604)*(N($B$107)+N($B$108))*N($B$110)+($B$112=$B$604)*(N($B$113)+N($B$114))*N($B$116)))</f>
+        <v/>
+      </c>
+      <c r="C878" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D878" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="18" t="inlineStr">
+        <is>
+          <t>Permuta financeira 1 — equivalente em R$</t>
+        </is>
+      </c>
+      <c r="B879" s="24">
+        <f>IF($B$609="pct_vgv",N($B$611)*$B$757,IF($B$609="rs",N($B$610),0))</f>
+        <v/>
+      </c>
+      <c r="C879" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D879" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="18" t="inlineStr">
+        <is>
+          <t>Permuta física 2 — VGV entregue (unidades × área × preço sugerido)</t>
+        </is>
+      </c>
+      <c r="B880" s="24">
+        <f>IF($B$606="",0,N($B$607)*(($B$58=$B$606)*(N($B$59)+N($B$60))*N($B$62)+($B$64=$B$606)*(N($B$65)+N($B$66))*N($B$68)+($B$70=$B$606)*(N($B$71)+N($B$72))*N($B$74)+($B$76=$B$606)*(N($B$77)+N($B$78))*N($B$80)+($B$82=$B$606)*(N($B$83)+N($B$84))*N($B$86)+($B$88=$B$606)*(N($B$89)+N($B$90))*N($B$92)+($B$94=$B$606)*(N($B$95)+N($B$96))*N($B$98)+($B$100=$B$606)*(N($B$101)+N($B$102))*N($B$104)+($B$106=$B$606)*(N($B$107)+N($B$108))*N($B$110)+($B$112=$B$606)*(N($B$113)+N($B$114))*N($B$116)))</f>
+        <v/>
+      </c>
+      <c r="C880" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D880" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="18" t="inlineStr">
+        <is>
+          <t>Permuta financeira 2 — equivalente em R$</t>
+        </is>
+      </c>
+      <c r="B881" s="24">
+        <f>IF($B$614="pct_vgv",N($B$616)*$B$757,IF($B$614="rs",N($B$615),0))</f>
+        <v/>
+      </c>
+      <c r="C881" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D881" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="18" t="inlineStr">
+        <is>
+          <t>Σ valor das dívidas</t>
+        </is>
+      </c>
+      <c r="B882" s="24">
+        <f>N($B$631)+N($B$644)+N($B$657)</f>
+        <v/>
+      </c>
+      <c r="C882" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D882" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="18" t="inlineStr">
+        <is>
           <t>Σ valor dos equities</t>
         </is>
       </c>
-      <c r="B854" s="24">
+      <c r="B883" s="24">
         <f>N($B$670)+N($B$677)+N($B$684)</f>
         <v/>
       </c>
-      <c r="C854" s="20" t="inlineStr">
+      <c r="C883" s="20" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-      <c r="D854" s="21" t="inlineStr">
+      <c r="D883" s="21" t="inlineStr">
         <is>
           <t>calculado</t>
         </is>
       </c>
     </row>
-    <row r="857">
-      <c r="F857" t="inlineStr">
+    <row r="886">
+      <c r="F886" t="inlineStr">
         <is>
           <t>Preço</t>
         </is>
       </c>
     </row>
-    <row r="858">
-      <c r="F858" t="inlineStr">
+    <row r="887">
+      <c r="F887" t="inlineStr">
         <is>
           <t>Registro</t>
         </is>
       </c>
     </row>
-    <row r="859">
-      <c r="F859" t="inlineStr">
+    <row r="888">
+      <c r="F888" t="inlineStr">
         <is>
           <t>Outro</t>
         </is>
       </c>
     </row>
-    <row r="860">
-      <c r="F860" t="inlineStr">
+    <row r="889">
+      <c r="F889" t="inlineStr">
         <is>
           <t>Construção</t>
         </is>
       </c>
     </row>
-    <row r="861">
-      <c r="F861" t="inlineStr">
+    <row r="890">
+      <c r="F890" t="inlineStr">
         <is>
           <t>Outorga</t>
         </is>
       </c>
     </row>
-    <row r="862">
-      <c r="F862" t="inlineStr">
+    <row r="891">
+      <c r="F891" t="inlineStr">
         <is>
           <t>Decoração</t>
         </is>
       </c>
     </row>
-    <row r="863">
-      <c r="F863" t="inlineStr">
+    <row r="892">
+      <c r="F892" t="inlineStr">
         <is>
           <t>Gestão da obra</t>
         </is>
       </c>
     </row>
-    <row r="864">
-      <c r="F864" t="inlineStr">
+    <row r="893">
+      <c r="F893" t="inlineStr">
         <is>
           <t>Contingência</t>
         </is>
       </c>
     </row>
-    <row r="865">
-      <c r="F865" t="inlineStr">
+    <row r="894">
+      <c r="F894" t="inlineStr">
         <is>
           <t>Marketing &amp; Publicidade</t>
         </is>
       </c>
     </row>
-    <row r="866">
-      <c r="F866" t="inlineStr">
+    <row r="895">
+      <c r="F895" t="inlineStr">
         <is>
           <t>Corretagem de vendas</t>
         </is>
       </c>
     </row>
-    <row r="867">
-      <c r="F867" t="inlineStr">
+    <row r="896">
+      <c r="F896" t="inlineStr">
         <is>
           <t>Projetos</t>
         </is>
       </c>
     </row>
-    <row r="868">
-      <c r="F868" t="inlineStr">
+    <row r="897">
+      <c r="F897" t="inlineStr">
         <is>
           <t>Licenças e Aprovações</t>
         </is>
       </c>
     </row>
-    <row r="869">
-      <c r="F869" t="inlineStr">
+    <row r="898">
+      <c r="F898" t="inlineStr">
         <is>
           <t>Manutenção pós-obra</t>
         </is>
       </c>
     </row>
-    <row r="870">
-      <c r="F870" t="inlineStr">
+    <row r="899">
+      <c r="F899" t="inlineStr">
         <is>
           <t>Marketing global</t>
         </is>
       </c>
     </row>
-    <row r="871">
-      <c r="F871" t="inlineStr">
+    <row r="900">
+      <c r="F900" t="inlineStr">
         <is>
           <t>Gestão</t>
         </is>
       </c>
     </row>
-    <row r="872">
-      <c r="F872" t="inlineStr">
+    <row r="901">
+      <c r="F901" t="inlineStr">
         <is>
           <t>Stand de vendas</t>
         </is>
       </c>
     </row>
-    <row r="873">
-      <c r="F873" t="inlineStr">
+    <row r="902">
+      <c r="F902" t="inlineStr">
         <is>
           <t>Juros de financiamento</t>
         </is>
       </c>
     </row>
-    <row r="874">
-      <c r="F874" t="inlineStr">
+    <row r="903">
+      <c r="F903" t="inlineStr">
         <is>
           <t>Taxas bancárias</t>
         </is>
       </c>
     </row>
-    <row r="875">
-      <c r="F875" t="inlineStr">
+    <row r="904">
+      <c r="F904" t="inlineStr">
         <is>
           <t>Estruturação de dívida</t>
         </is>
       </c>
     </row>
-    <row r="876">
-      <c r="F876" t="inlineStr">
+    <row r="905">
+      <c r="F905" t="inlineStr">
         <is>
           <t>Investidores</t>
         </is>
       </c>
     </row>
-    <row r="878">
-      <c r="F878" t="inlineStr">
+    <row r="907">
+      <c r="F907" t="inlineStr">
         <is>
           <t>planejamento</t>
         </is>
       </c>
     </row>
-    <row r="879">
-      <c r="F879" t="inlineStr">
+    <row r="908">
+      <c r="F908" t="inlineStr">
         <is>
           <t>pre_lancamento</t>
         </is>
       </c>
     </row>
-    <row r="880">
-      <c r="F880" t="inlineStr">
+    <row r="909">
+      <c r="F909" t="inlineStr">
         <is>
           <t>lancamento</t>
         </is>
       </c>
     </row>
-    <row r="881">
-      <c r="F881" t="inlineStr">
+    <row r="910">
+      <c r="F910" t="inlineStr">
         <is>
           <t>obra</t>
         </is>
       </c>
     </row>
-    <row r="882">
-      <c r="F882" t="inlineStr">
+    <row r="911">
+      <c r="F911" t="inlineStr">
         <is>
           <t>pos_obra</t>
         </is>
       </c>
     </row>
-    <row r="883">
-      <c r="F883" t="inlineStr">
+    <row r="912">
+      <c r="F912" t="inlineStr">
         <is>
           <t>customizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Curva S</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>unit_delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>sales_revenue</t>
         </is>
       </c>
     </row>
@@ -15565,7 +16202,7 @@
     <mergeCell ref="A449:D449"/>
     <mergeCell ref="A160:D160"/>
   </mergeCells>
-  <dataValidations count="22">
+  <dataValidations count="23">
     <dataValidation sqref="B5 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="No máximo 200 caracteres." type="textLength" errorStyle="warning" operator="lessThanOrEqual">
       <formula1>200</formula1>
     </dataValidation>
@@ -15621,14 +16258,17 @@
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
+    <dataValidation sqref="B302 B313 B324 B335 B346 B357 B368 B379 B390 B401 B412 B423 B434 B445 B456 B467 B478 B489 B500 B511 B522 B533 B544 B555 B566 B577 B588 B599" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
+      <formula1>$F$914:$F$917</formula1>
+    </dataValidation>
     <dataValidation sqref="B303 B314 B325 B336 B347 B358 B369 B380 B391 B402 B413 B424 B435 B446 B457 B468 B479 B490 B501 B512 B523 B534 B545 B556 B567 B578 B589 B600 B632 B645 B658 B671 B678 B685" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
-      <formula1>$F$878:$F$883</formula1>
+      <formula1>$F$907:$F$912</formula1>
     </dataValidation>
     <dataValidation sqref="B329 B340 B351 B362 B373 B384 B395 B406 B417 B428 B439 B450 B461 B472 B483 B494 B505 B516 B527 B538 B549 B560 B571 B582 B593" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"terreno,obra,diretos,indireto,financeiro"</formula1>
     </dataValidation>
     <dataValidation sqref="B330 B341 B352 B363 B374 B385 B396 B407 B418 B429 B440 B451 B462 B473 B484 B495 B506 B517 B528 B539 B550 B561 B572 B583 B594" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
-      <formula1>$F$857:$F$876</formula1>
+      <formula1>$F$886:$F$905</formula1>
     </dataValidation>
     <dataValidation sqref="B609 B614" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"rs,pct_vgv"</formula1>

--- a/referencia/formularios/formulario-avancado-loteamento.xlsx
+++ b/referencia/formularios/formulario-avancado-loteamento.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>lista: manual (inserir novo) | nucleo (buscar terreno)</t>
+          <t>lista: manual (inserir novo) | nucleo (buscar terreno — o importador só aceita manual)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -5293,7 +5293,7 @@
     <row r="293" ht="117" customHeight="1">
       <c r="A293" s="12" t="inlineStr">
         <is>
-          <t>Categorias e unidades aceitas (rs = R$ · rs_m2_priv = R$/m² privativo · rs_m2_terreno · pct_vgv · pct_receita · pct_obra · pct_recebido · pct_constr). TERRENO: Preço (rs, rs_m2_terreno; permuta financeira: rs, pct_vgv) · Registro (rs, rs_m2_priv) · Outro (rs, pct_vgv). OBRA: Construção, Decoração (rs, rs_m2_priv) · Outorga, Contingência, Outro (rs, pct_vgv) · Gestão da obra (rs, pct_obra). DIRETOS: Marketing &amp; Publicidade, Manutenção pós-obra, Outro (rs, pct_vgv, pct_recebido) · Corretagem de vendas (pct_vgv) · Projetos (rs, rs_m2_priv, pct_constr) · Licenças e Aprovações (rs, rs_m2_priv). INDIRETO: Marketing global, Gestão, Outro (rs, pct_vgv, pct_recebido) · Stand de vendas (rs, pct_vgv). FINANCEIRO: Juros de financiamento, Taxas bancárias, Estruturação de dívida, Investidores, Outro (rs, pct_vgv). Cronograma padrão: terreno/Preço = customizado; terreno/demais, indireto = planejamento; obra/diretos/financeiro = obra; Manutenção pós-obra = pos_obra. Início e Duração só valem com cronograma = customizado; cronograma ancorado em fase customizada = escrever "fase: &lt;nome da fase&gt;". Corretagem sai no mês da venda e a permuta física na entrega das unidades (não escolhem distribuição). Obrigatórias: terreno/Preço, obra/Construção, diretos/Corretagem de vendas (% VGV).</t>
+          <t>Categorias e unidades aceitas (rs = R$ · rs_m2_priv = R$/m² privativo · rs_m2_terreno · pct_vgv · pct_obra · pct_recebido · pct_constr). TERRENO: Preço (rs, rs_m2_terreno; permuta financeira: rs, pct_vgv) · Registro (rs, rs_m2_priv) · Outro (rs, pct_vgv). OBRA: Construção, Decoração (rs, rs_m2_priv) · Outorga, Contingência, Outro (rs, pct_vgv) · Gestão da obra (rs, pct_obra). DIRETOS: Marketing &amp; Publicidade, Manutenção pós-obra, Outro (rs, pct_vgv, pct_recebido) · Corretagem de vendas (pct_vgv) · Projetos (rs, rs_m2_priv, pct_constr) · Licenças e Aprovações (rs, rs_m2_priv). INDIRETO: Marketing global, Gestão, Outro (rs, pct_vgv, pct_recebido) · Stand de vendas (rs, pct_vgv). FINANCEIRO: Juros de financiamento, Taxas bancárias, Estruturação de dívida, Investidores, Outro (rs, pct_vgv). Cronograma padrão: terreno/Preço = customizado; terreno/demais, indireto = planejamento; obra/diretos/financeiro = obra; Manutenção pós-obra = pos_obra. Início e Duração só valem com cronograma = customizado; cronograma ancorado em fase customizada = escrever "fase: &lt;nome da fase&gt;". Corretagem sai no mês da venda e a permuta física na entrega das unidades (não escolhem distribuição). Obrigatórias: terreno/Preço, obra/Construção, diretos/Corretagem de vendas (% VGV).</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       <c r="B299" s="6" t="n"/>
       <c r="C299" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
@@ -5575,7 +5575,7 @@
       <c r="B310" s="6" t="n"/>
       <c r="C310" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D310" s="8" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D321" s="8" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="B332" s="6" t="n"/>
       <c r="C332" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D332" s="8" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="B343" s="6" t="n"/>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D343" s="8" t="inlineStr">
@@ -6327,7 +6327,7 @@
       <c r="B354" s="6" t="n"/>
       <c r="C354" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D354" s="8" t="inlineStr">
@@ -6512,7 +6512,7 @@
       <c r="B365" s="6" t="n"/>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D365" s="8" t="inlineStr">
@@ -6697,7 +6697,7 @@
       <c r="B376" s="6" t="n"/>
       <c r="C376" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D376" s="8" t="inlineStr">
@@ -6882,7 +6882,7 @@
       <c r="B387" s="6" t="n"/>
       <c r="C387" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D387" s="8" t="inlineStr">
@@ -7067,7 +7067,7 @@
       <c r="B398" s="6" t="n"/>
       <c r="C398" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D398" s="8" t="inlineStr">
@@ -7252,7 +7252,7 @@
       <c r="B409" s="6" t="n"/>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D409" s="8" t="inlineStr">
@@ -7437,7 +7437,7 @@
       <c r="B420" s="6" t="n"/>
       <c r="C420" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D420" s="8" t="inlineStr">
@@ -7622,7 +7622,7 @@
       <c r="B431" s="6" t="n"/>
       <c r="C431" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D431" s="8" t="inlineStr">
@@ -7807,7 +7807,7 @@
       <c r="B442" s="6" t="n"/>
       <c r="C442" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D442" s="8" t="inlineStr">
@@ -7992,7 +7992,7 @@
       <c r="B453" s="6" t="n"/>
       <c r="C453" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D453" s="8" t="inlineStr">
@@ -8177,7 +8177,7 @@
       <c r="B464" s="6" t="n"/>
       <c r="C464" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D464" s="8" t="inlineStr">
@@ -8362,7 +8362,7 @@
       <c r="B475" s="6" t="n"/>
       <c r="C475" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D475" s="8" t="inlineStr">
@@ -8547,7 +8547,7 @@
       <c r="B486" s="6" t="n"/>
       <c r="C486" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D486" s="8" t="inlineStr">
@@ -8732,7 +8732,7 @@
       <c r="B497" s="6" t="n"/>
       <c r="C497" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D497" s="8" t="inlineStr">
@@ -8917,7 +8917,7 @@
       <c r="B508" s="6" t="n"/>
       <c r="C508" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D508" s="8" t="inlineStr">
@@ -9102,7 +9102,7 @@
       <c r="B519" s="6" t="n"/>
       <c r="C519" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D519" s="8" t="inlineStr">
@@ -9287,7 +9287,7 @@
       <c r="B530" s="6" t="n"/>
       <c r="C530" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D530" s="8" t="inlineStr">
@@ -9472,7 +9472,7 @@
       <c r="B541" s="6" t="n"/>
       <c r="C541" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D541" s="8" t="inlineStr">
@@ -9657,7 +9657,7 @@
       <c r="B552" s="6" t="n"/>
       <c r="C552" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D552" s="8" t="inlineStr">
@@ -9842,7 +9842,7 @@
       <c r="B563" s="6" t="n"/>
       <c r="C563" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D563" s="8" t="inlineStr">
@@ -10027,7 +10027,7 @@
       <c r="B574" s="6" t="n"/>
       <c r="C574" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D574" s="8" t="inlineStr">
@@ -10212,7 +10212,7 @@
       <c r="B585" s="6" t="n"/>
       <c r="C585" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D585" s="8" t="inlineStr">
@@ -10397,7 +10397,7 @@
       <c r="B596" s="6" t="n"/>
       <c r="C596" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D596" s="8" t="inlineStr">
@@ -16252,7 +16252,7 @@
       <formula1>"Entrada,Parcelamento"</formula1>
     </dataValidation>
     <dataValidation sqref="B299 B310 B332 B343 B354 B365 B376 B387 B398 B409 B420 B431 B442 B453 B464 B475 B486 B497 B508 B519 B530 B541 B552 B563 B574 B585 B596" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
-      <formula1>"rs,rs_m2_priv,rs_m2_terreno,pct_vgv,pct_receita,pct_obra,pct_recebido,pct_constr"</formula1>
+      <formula1>"rs,rs_m2_priv,rs_m2_terreno,pct_vgv,pct_obra,pct_recebido,pct_constr"</formula1>
     </dataValidation>
     <dataValidation sqref="B301 B312 B323 B334 B345 B356 B367 B378 B389 B400 B411 B422 B433 B444 B455 B466 B477 B488 B499 B510 B521 B532 B543 B554 B565 B576 B587 B598" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 10)." type="decimal" errorStyle="warning" operator="between">
       <formula1>0</formula1>

--- a/referencia/formularios/formulario-avancado-loteamento.xlsx
+++ b/referencia/formularios/formulario-avancado-loteamento.xlsx
@@ -600,7 +600,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %). O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
+          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite com o símbolo % (4%), nunca só o número. O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
         </is>
       </c>
     </row>

--- a/referencia/formularios/formulario-avancado-loteamento.xlsx
+++ b/referencia/formularios/formulario-avancado-loteamento.xlsx
@@ -2480,7 +2480,7 @@
     <row r="119" ht="39" customHeight="1">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t>Saldo de chaves = o Repasse acima. "Repasse bancário" é a parte dele paga pelo banco no mês seguinte ao fim da obra (vazio = 100%, tudo no banco). O resto vira carteira própria: a empresa financia o comprador em N parcelas mensais Price com os Juros de tabela, a partir do mês seguinte ao fim da obra + a carência. Loteamento sem banco: 0%.</t>
+          <t>Saldo de chaves = o Repasse acima. "Repasse bancário" é a parte dele paga pelo banco no mês seguinte ao fim da obra (vazio = 100%, tudo no banco). O resto vira carteira própria: a empresa financia o comprador em N parcelas mensais Price com os Juros de tabela, a partir do mês seguinte ao fim da obra + a carência (nunca antes do mês seguinte à venda): também a venda feita depois da entrega tem essa parte financiada. Loteamento sem banco: 0%.</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A175:D175"/>
   </mergeCells>
-  <dataValidations count="23">
+  <dataValidations count="24">
     <dataValidation sqref="B5 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="No máximo 200 caracteres." type="textLength" errorStyle="warning" operator="lessThanOrEqual">
       <formula1>200</formula1>
     </dataValidation>
@@ -17070,7 +17070,7 @@
       <formula1>0</formula1>
       <formula2>9.9999</formula2>
     </dataValidation>
-    <dataValidation sqref="B20 B23 B122 B123 B124 B128 B133 B134 B135 B139 B144 B145 B146 B150 B155 B156 B157 B161 B166 B167 B168 B172 B180 B182 B183 B188 B190 B191 B196 B198 B199 B204 B206 B207 B212 B214 B215 B220 B222 B223 B228 B230 B231 B236 B238 B239 B244 B246 B247 B252 B254 B255 B627 B632 B640 B641 B642 B652 B655 B665 B668 B678 B681 B690 B697 B704 B710 B711 B712 B719 B720 B721 B728 B729 B730" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 1)." type="decimal" errorStyle="warning" operator="between">
+    <dataValidation sqref="B20 B23 B122 B123 B124 B128 B133 B134 B135 B139 B144 B145 B146 B150 B155 B156 B157 B161 B166 B167 B168 B172 B180 B182 B183 B188 B190 B191 B196 B198 B199 B204 B206 B207 B212 B214 B215 B220 B222 B223 B228 B230 B231 B236 B238 B239 B244 B246 B247 B252 B254 B255 B627 B632 B640 B641 B642 B652 B655 B665 B668 B678 B681 B690 B697 B704 B711 B712 B720 B721 B729 B730" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 1)." type="decimal" errorStyle="warning" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -17123,6 +17123,10 @@
     <dataValidation sqref="B689 B696 B703" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"permuta_financeira,resultado_final"</formula1>
     </dataValidation>
+    <dataValidation sqref="B710 B719 B728" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0.0001 a 1)." type="decimal" errorStyle="warning" operator="between">
+      <formula1>0.0001</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
     <dataValidation sqref="B735 B736 B738 B739 B741 B742 B744 B745 B747 B748" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (-1 a 10)." type="decimal" errorStyle="warning" operator="between">
       <formula1>-1</formula1>
       <formula2>10</formula2>
